--- a/docs/business/MichiganLTC_Network_Financial_Model_FINAL.xlsx
+++ b/docs/business/MichiganLTC_Network_Financial_Model_FINAL.xlsx
@@ -9,10 +9,11 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per_Site" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Network" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raises" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Caveats" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opex_BuildUp" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per_Site" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Network" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raises" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Caveats" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,6 +57,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007A1F1F"/>
     </font>
   </fonts>
   <fills count="6">
@@ -112,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -128,21 +133,22 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -680,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1034,16 +1040,16 @@
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>opex</t>
+          <t>labor_fl</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Annual operating cost (ex-credits, steady state)</t>
+          <t>Site labor — total loaded, 62 FTE (FL basis)</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>5381149</v>
+        <v>5522400</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1052,198 +1058,198 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>implied from signed model (rev-EBITDA) [CONFIRM build-up]</t>
+          <t>WasteWerx Staffing Pro Forma (uploaded); FL market</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>raise_site</t>
+          <t>mi_adj</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Project raise per site</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>15000000</v>
+          <t>Michigan labor adjustment factor</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>1.05</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>x</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>sponsor-directed headline</t>
+          <t>FL-&gt;MI cost-of-living [CONFIRM]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>feedstock</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Use of funds: build / core plant</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>8000000</v>
+          <t>Net feedstock cost (negative if tipping-fee positive)</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>rough verbal</t>
+          <t>[CONFIRM — tires may carry tipping fees]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>addl</t>
+          <t>utilities</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Use of funds: added construction</t>
+          <t>Utilities / energy (net of syngas self-supply)</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>1000000</v>
+        <v>1200000</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>rough verbal</t>
+          <t>ESTIMATE [CONFIRM]</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>preproc</t>
+          <t>maint</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Use of funds: pre-processing/pre-treatment equip</t>
+          <t>Maintenance materials + contract maintenance</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>2000000</v>
+        <v>500000</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>rough verbal</t>
+          <t>ESTIMATE [CONFIRM]</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>conting</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Use of funds: contingency/fees/payroll/training</t>
+          <t>Insurance (industrial)</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>5000000</v>
+        <v>400000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>rough verbal</t>
+          <t>ESTIMATE [CONFIRM]</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>ww_license</t>
+          <t>contracted</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WasteWerx license fee (Yr1, net of design credit)</t>
+          <t>Contracted svcs (security/janitorial/IT/3rd-party MRV verification)</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>5450000</v>
+        <v>350000</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>signed Model 3</t>
+          <t>NOT in staffing pro forma — budget separately [CONFIRM]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>ww_design</t>
+          <t>ga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>WasteWerx design fee (credited)</t>
+          <t>G&amp;A / SG&amp;A (corporate alloc, legal, accounting, software)</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>50000</v>
+        <v>750000</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>signed Model 3</t>
+          <t>ESTIMATE [CONFIRM]</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>ww_monitor</t>
+          <t>raise_site</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>WasteWerx Yr1 monitoring fees</t>
+          <t>Project raise per site</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>175000</v>
+        <v>15000000</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1252,23 +1258,23 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>signed Model 3</t>
+          <t>sponsor-directed headline</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>ww_royalty</t>
+          <t>build</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>WasteWerx Yr1 production royalty</t>
+          <t>Use of funds: build / core plant</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>995328</v>
+        <v>8000000</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1277,23 +1283,23 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>signed Model 3</t>
+          <t>rough verbal</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>cust_capex</t>
+          <t>addl</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Customer-side capex (site/utilities/permits/WC)</t>
+          <t>Use of funds: added construction</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>952500</v>
+        <v>1000000</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1302,23 +1308,23 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>signed Model 3</t>
+          <t>rough verbal</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>company_raise</t>
+          <t>preproc</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Company-level raise (separate)</t>
+          <t>Use of funds: pre-processing/pre-treatment equip</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>2500000</v>
+        <v>2000000</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1327,30 +1333,205 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>sponsor-directed</t>
+          <t>rough verbal</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>conting</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Use of funds: contingency/fees/payroll/training</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>rough verbal</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>ww_license</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>WasteWerx license fee (Yr1, net of design credit)</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>5450000</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>signed Model 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>ww_design</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>WasteWerx design fee (credited)</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>signed Model 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>ww_monitor</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>WasteWerx Yr1 monitoring fees</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>175000</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>signed Model 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>ww_royalty</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>WasteWerx Yr1 production royalty</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>995328</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>signed Model 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>cust_capex</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Customer-side capex (site/utilities/permits/WC)</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>952500</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>signed Model 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>company_raise</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Company-level raise (separate)</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>sponsor-directed</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
           <t>sites</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>Number of sites in network</t>
         </is>
       </c>
-      <c r="C29" s="6" t="n">
+      <c r="C36" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D36" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Michigan corridor</t>
         </is>
@@ -1362,6 +1543,250 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Annual operating cost — bottom-up (per site, steady state)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>KEY FINDING: site labor ALONE exceeds the signed model's entire implied opex. Green = known, orange = estimate to confirm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Cost line</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Amount $/yr</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Site labor — loaded, 62 FTE (MI-adjusted)</t>
+        </is>
+      </c>
+      <c r="B5" s="10">
+        <f>Inputs!$C$17*Inputs!$C$18</f>
+        <v/>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>KNOWN — WasteWerx staffing pro forma</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>WasteWerx production royalty (recurring)</t>
+        </is>
+      </c>
+      <c r="B6" s="10">
+        <f>Inputs!$C$33</f>
+        <v/>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>KNOWN — signed model</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>WasteWerx monitoring fees (recurring)</t>
+        </is>
+      </c>
+      <c r="B7" s="10">
+        <f>Inputs!$C$32</f>
+        <v/>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>KNOWN — signed model</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Net feedstock cost</t>
+        </is>
+      </c>
+      <c r="B8" s="11">
+        <f>Inputs!$C$19</f>
+        <v/>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>[CONFIRM — may be tipping-fee positive]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Utilities / energy (net of syngas self-supply)</t>
+        </is>
+      </c>
+      <c r="B9" s="11">
+        <f>Inputs!$C$20</f>
+        <v/>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>ESTIMATE [CONFIRM]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Maintenance materials + contract maintenance</t>
+        </is>
+      </c>
+      <c r="B10" s="11">
+        <f>Inputs!$C$21</f>
+        <v/>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>ESTIMATE [CONFIRM]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Insurance (industrial)</t>
+        </is>
+      </c>
+      <c r="B11" s="11">
+        <f>Inputs!$C$22</f>
+        <v/>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>ESTIMATE [CONFIRM]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Contracted services (security/janitorial/IT/3rd-party MRV)</t>
+        </is>
+      </c>
+      <c r="B12" s="11">
+        <f>Inputs!$C$23</f>
+        <v/>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>NOT in staffing pro forma [CONFIRM]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>G&amp;A / SG&amp;A</t>
+        </is>
+      </c>
+      <c r="B13" s="11">
+        <f>Inputs!$C$24</f>
+        <v/>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>ESTIMATE [CONFIRM]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>TOTAL ANNUAL OPEX (bottom-up)</t>
+        </is>
+      </c>
+      <c r="B14" s="13">
+        <f>SUM(B5:B13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Signed model's IMPLIED opex (rev - EBITDA)</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>5381149</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Understatement baked into signed EBITDA (bottom-up - implied)</t>
+        </is>
+      </c>
+      <c r="B17" s="16">
+        <f>B14-B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Labor ALONE (MI-adjusted)</t>
+        </is>
+      </c>
+      <c r="B19" s="17">
+        <f>Inputs!$C$17*Inputs!$C$18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="inlineStr">
+        <is>
+          <t>-&gt; exceeds the signed model's entire implied opex above. Signed EBITDA overstates margin.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1423,7 +1848,7 @@
         <f>(Inputs!$C$5*Inputs!$C$6*Inputs!$C$7)*Inputs!$C$9</f>
         <v/>
       </c>
-      <c r="C5" s="11" t="inlineStr">
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>BASE (conservative)</t>
         </is>
@@ -1444,7 +1869,7 @@
         <f>(Inputs!$C$5*Inputs!$C$6*Inputs!$C$8)*Inputs!$C$10</f>
         <v/>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>BASE</t>
         </is>
@@ -1465,7 +1890,7 @@
         <f>Inputs!$C$11</f>
         <v/>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>BASE (upgraded)</t>
         </is>
@@ -1486,7 +1911,7 @@
         <f>Inputs!$C$12</f>
         <v/>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>BASE (upgraded)</t>
         </is>
@@ -1503,11 +1928,11 @@
           <t>D4 RIN</t>
         </is>
       </c>
-      <c r="B9" s="12">
+      <c r="B9" s="11">
         <f>Inputs!$C$13</f>
         <v/>
       </c>
-      <c r="C9" s="11" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>CONTINGENT UPSIDE</t>
         </is>
@@ -1524,11 +1949,11 @@
           <t>D7 RIN</t>
         </is>
       </c>
-      <c r="B10" s="12">
+      <c r="B10" s="11">
         <f>Inputs!$C$14</f>
         <v/>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>CONTINGENT UPSIDE</t>
         </is>
@@ -1545,11 +1970,11 @@
           <t>Section 45Z — RD</t>
         </is>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="11">
         <f>Inputs!$C$15</f>
         <v/>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>CONTINGENT UPSIDE</t>
         </is>
@@ -1566,11 +1991,11 @@
           <t>Section 45Z — SAF</t>
         </is>
       </c>
-      <c r="B12" s="12">
+      <c r="B12" s="11">
         <f>Inputs!$C$16</f>
         <v/>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>CONTINGENT UPSIDE</t>
         </is>
@@ -1621,19 +2046,19 @@
           <t>Base — Conservative (raw oil + carbon black)</t>
         </is>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="20">
         <f>B5+B6</f>
         <v/>
       </c>
-      <c r="C16" s="13">
-        <f>Inputs!$C$17</f>
-        <v/>
-      </c>
-      <c r="D16" s="14">
+      <c r="C16" s="20">
+        <f>Opex_BuildUp!$B$14</f>
+        <v/>
+      </c>
+      <c r="D16" s="21">
         <f>B16-C16</f>
         <v/>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1645,19 +2070,19 @@
           <t>Base — Upgraded (RD + SAF + carbon black)</t>
         </is>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="20">
         <f>B7+B8+B6</f>
         <v/>
       </c>
-      <c r="C17" s="13">
-        <f>Inputs!$C$17</f>
-        <v/>
-      </c>
-      <c r="D17" s="14">
+      <c r="C17" s="20">
+        <f>Opex_BuildUp!$B$14</f>
+        <v/>
+      </c>
+      <c r="D17" s="21">
         <f>B17-C17</f>
         <v/>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -1669,19 +2094,19 @@
           <t>Signed headline (RD + SAF + credits, no carbon black)</t>
         </is>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="20">
         <f>B7+B8+B9+B10+B11+B12</f>
         <v/>
       </c>
-      <c r="C18" s="13">
-        <f>Inputs!$C$17</f>
-        <v/>
-      </c>
-      <c r="D18" s="15">
+      <c r="C18" s="20">
+        <f>Opex_BuildUp!$B$14</f>
+        <v/>
+      </c>
+      <c r="D18" s="22">
         <f>B18-C18</f>
         <v/>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="19" t="inlineStr">
         <is>
           <t>YES — ~$20.4M credit-dependent</t>
         </is>
@@ -1693,31 +2118,31 @@
           <t>Full stack (upgraded fuel + carbon black + credits)</t>
         </is>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="20">
         <f>B6+B7+B8+B9+B10+B11+B12</f>
         <v/>
       </c>
-      <c r="C19" s="13">
-        <f>Inputs!$C$17</f>
-        <v/>
-      </c>
-      <c r="D19" s="15">
+      <c r="C19" s="20">
+        <f>Opex_BuildUp!$B$14</f>
+        <v/>
+      </c>
+      <c r="D19" s="22">
         <f>B19-C19</f>
         <v/>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="19" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
         <is>
           <t>Contingent credit value at risk in headline (RIN + 45Z)</t>
         </is>
       </c>
-      <c r="B21" s="17">
+      <c r="B21" s="16">
         <f>B9+B10+B11+B12</f>
         <v/>
       </c>
@@ -1740,8 +2165,8 @@
           <t>Project raise per site</t>
         </is>
       </c>
-      <c r="B24" s="18">
-        <f>Inputs!$C$18</f>
+      <c r="B24" s="15">
+        <f>Inputs!$C$25</f>
         <v/>
       </c>
     </row>
@@ -1751,8 +2176,8 @@
           <t>WasteWerx Year 1 (license+design+monitoring+royalty)</t>
         </is>
       </c>
-      <c r="B25" s="18">
-        <f>Inputs!$C$23+Inputs!$C$24+Inputs!$C$25+Inputs!$C$26</f>
+      <c r="B25" s="15">
+        <f>Inputs!$C$30+Inputs!$C$31+Inputs!$C$32+Inputs!$C$33</f>
         <v/>
       </c>
     </row>
@@ -1762,35 +2187,35 @@
           <t>Customer-side capex</t>
         </is>
       </c>
-      <c r="B26" s="18">
-        <f>Inputs!$C$27</f>
+      <c r="B26" s="15">
+        <f>Inputs!$C$34</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>Total Year 1 cash out</t>
         </is>
       </c>
-      <c r="B27" s="19">
+      <c r="B27" s="17">
         <f>B25+B26</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>Residual project envelope (land, civil, integration, contingency, payroll, reserves)</t>
         </is>
       </c>
-      <c r="B28" s="21">
+      <c r="B28" s="13">
         <f>B24-B27</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
         <is>
           <t>Use-of-funds (sponsor rough) vs raise — RECONCILE</t>
         </is>
@@ -1802,8 +2227,8 @@
           <t>Build + added construction + pre-processing + contingency</t>
         </is>
       </c>
-      <c r="B31" s="18">
-        <f>Inputs!$C$19+Inputs!$C$20+Inputs!$C$21+Inputs!$C$22</f>
+      <c r="B31" s="15">
+        <f>Inputs!$C$26+Inputs!$C$27+Inputs!$C$28+Inputs!$C$29</f>
         <v/>
       </c>
     </row>
@@ -1813,8 +2238,8 @@
           <t>Reconciliation gap vs $15M raise (negative = over)</t>
         </is>
       </c>
-      <c r="B32" s="22">
-        <f>Inputs!$C$18-B31</f>
+      <c r="B32" s="23">
+        <f>Inputs!$C$25-B31</f>
         <v/>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1828,7 +2253,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1891,15 +2316,15 @@
           <t>Base EBITDA — Conservative</t>
         </is>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="20">
         <f>'Per_Site'!D16</f>
         <v/>
       </c>
-      <c r="C5" s="11">
-        <f>Inputs!$C$29</f>
-        <v/>
-      </c>
-      <c r="D5" s="14">
+      <c r="C5" s="19">
+        <f>Inputs!$C$36</f>
+        <v/>
+      </c>
+      <c r="D5" s="21">
         <f>B5*C5</f>
         <v/>
       </c>
@@ -1915,15 +2340,15 @@
           <t>Base EBITDA — Upgraded</t>
         </is>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="20">
         <f>'Per_Site'!D17</f>
         <v/>
       </c>
-      <c r="C6" s="11">
-        <f>Inputs!$C$29</f>
-        <v/>
-      </c>
-      <c r="D6" s="14">
+      <c r="C6" s="19">
+        <f>Inputs!$C$36</f>
+        <v/>
+      </c>
+      <c r="D6" s="21">
         <f>B6*C6</f>
         <v/>
       </c>
@@ -1939,15 +2364,15 @@
           <t>Signed-headline EBITDA (credit-dependent)</t>
         </is>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="20">
         <f>'Per_Site'!D18</f>
         <v/>
       </c>
-      <c r="C7" s="11">
-        <f>Inputs!$C$29</f>
-        <v/>
-      </c>
-      <c r="D7" s="15">
+      <c r="C7" s="19">
+        <f>Inputs!$C$36</f>
+        <v/>
+      </c>
+      <c r="D7" s="22">
         <f>B7*C7</f>
         <v/>
       </c>
@@ -1963,15 +2388,15 @@
           <t>Signed-headline revenue</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="20">
         <f>'Per_Site'!B18</f>
         <v/>
       </c>
-      <c r="C8" s="11">
-        <f>Inputs!$C$29</f>
-        <v/>
-      </c>
-      <c r="D8" s="15">
+      <c r="C8" s="19">
+        <f>Inputs!$C$36</f>
+        <v/>
+      </c>
+      <c r="D8" s="22">
         <f>B8*C8</f>
         <v/>
       </c>
@@ -1987,15 +2412,15 @@
           <t>Contingent credit value at risk</t>
         </is>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="20">
         <f>'Per_Site'!B21</f>
         <v/>
       </c>
-      <c r="C9" s="11">
-        <f>Inputs!$C$29</f>
-        <v/>
-      </c>
-      <c r="D9" s="15">
+      <c r="C9" s="19">
+        <f>Inputs!$C$36</f>
+        <v/>
+      </c>
+      <c r="D9" s="22">
         <f>B9*C9</f>
         <v/>
       </c>
@@ -2011,15 +2436,15 @@
           <t>Year 1 cash out</t>
         </is>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="20">
         <f>'Per_Site'!B27</f>
         <v/>
       </c>
-      <c r="C10" s="11">
-        <f>Inputs!$C$29</f>
-        <v/>
-      </c>
-      <c r="D10" s="14">
+      <c r="C10" s="19">
+        <f>Inputs!$C$36</f>
+        <v/>
+      </c>
+      <c r="D10" s="21">
         <f>B10*C10</f>
         <v/>
       </c>
@@ -2035,15 +2460,15 @@
           <t>Project raises (sites x $15M)</t>
         </is>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="20">
         <f>'Per_Site'!B24</f>
         <v/>
       </c>
-      <c r="C11" s="11">
-        <f>Inputs!$C$29</f>
-        <v/>
-      </c>
-      <c r="D11" s="14">
+      <c r="C11" s="19">
+        <f>Inputs!$C$36</f>
+        <v/>
+      </c>
+      <c r="D11" s="21">
         <f>B11*C11</f>
         <v/>
       </c>
@@ -2058,7 +2483,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2104,13 +2529,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="23" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>Project raise per site</t>
         </is>
       </c>
-      <c r="B5" s="24">
-        <f>Inputs!$C$18</f>
+      <c r="B5" s="25">
+        <f>Inputs!$C$25</f>
         <v/>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -2120,13 +2545,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="24" t="inlineStr">
         <is>
           <t>Project raises — 3 sites</t>
         </is>
       </c>
-      <c r="B6" s="24">
-        <f>Inputs!$C$18*Inputs!$C$29</f>
+      <c r="B6" s="25">
+        <f>Inputs!$C$25*Inputs!$C$36</f>
         <v/>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -2136,13 +2561,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>Company-level raise (separate)</t>
         </is>
       </c>
-      <c r="B7" s="24">
-        <f>Inputs!$C$28</f>
+      <c r="B7" s="25">
+        <f>Inputs!$C$35</f>
         <v/>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -2152,13 +2577,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Combined discussion envelope</t>
         </is>
       </c>
-      <c r="B8" s="24">
-        <f>Inputs!$C$18*Inputs!$C$29+Inputs!$C$28</f>
+      <c r="B8" s="25">
+        <f>Inputs!$C$25*Inputs!$C$36+Inputs!$C$35</f>
         <v/>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -2172,13 +2597,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="116" customWidth="1" min="1" max="1"/>
@@ -2260,91 +2685,119 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Operating cost ($5.38M) is implied (rev - EBITDA) from the signed model; obtain the line-item build-up [CONFIRM].</t>
+          <t xml:space="preserve">  * OPEX IS UNDERSTATED IN THE SIGNED MODEL. The uploaded WasteWerx staffing pro forma shows 62 FTE / $5.52M loaded</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    labor alone — more than the signed model's entire implied opex ($5.38M). Bottom-up opex (Opex_BuildUp sheet) is</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>CAPITAL</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    materially higher; utilities/maintenance/insurance/contracted/G&amp;A are estimates [CONFIRM with WasteWerx].</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Sponsor use-of-funds (~$16M) exceeds the $15M/site raise by ~$1M — confirm which line absorbs it.</t>
+          <t xml:space="preserve">  * Contracted services (security, janitorial, IT/MSP, certified 3rd-party MRV verification) are explicitly NOT in the</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * $2.5M company raise stays separate from site SPV totals.</t>
+          <t xml:space="preserve">    staffing pro forma and must be budgeted separately. Labor figure is FL market; add 5-10% for Michigan.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * WasteWerx is a LICENSE, not a sale; title stays with WasteWerx; license fee depreciation differs; transfer/termination terms matter.</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>CAPITAL</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>GOVERNANCE / LEGAL</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Sponsor use-of-funds (~$16M) exceeds the $15M/site raise by ~$1M — confirm which line absorbs it.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Securities: not an offer; securities counsel review required before any circulation.</t>
+          <t xml:space="preserve">  * $2.5M company raise stays separate from site SPV totals.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * PublicLogic = governance/document partner, NOT placement agent/broker-dealer; fee FIXED &amp; NON-CONTINGENT.</t>
+          <t xml:space="preserve">  * WasteWerx is a LICENSE, not a sale; title stays with WasteWerx; license fee depreciation differs; transfer/termination terms matter.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * Community-benefit %: source files say 10%; sponsor flags a conflict — do not publish a number until reconciled.</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * Final site list (Coldwater Phase 2 vs Lincoln) [CONFIRM]; parent-holdco legal name [CONFIRM].</t>
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>GOVERNANCE / LEGAL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * National Salvage: 'largest treated-wood recycler in the U.S.' unless stronger evidence (a verbal 'in the world' is unverified).</t>
+          <t xml:space="preserve">  * Securities: not an offer; securities counsel review required before any circulation.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * PublicLogic = governance/document partner, NOT placement agent/broker-dealer; fee FIXED &amp; NON-CONTINGENT.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Community-benefit %: source files say 10%; sponsor flags a conflict — do not publish a number until reconciled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Final site list (Coldwater Phase 2 vs Lincoln) [CONFIRM]; parent-holdco legal name [CONFIRM].</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * National Salvage: 'largest treated-wood recycler in the U.S.' unless stronger evidence (a verbal 'in the world' is unverified).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>Not financial, accounting, securities, or tax advice. Figures trace to the canonical workbook / signed pro forma; verify before use.</t>
         </is>

--- a/docs/business/MichiganLTC_Network_Financial_Model_FINAL.xlsx
+++ b/docs/business/MichiganLTC_Network_Financial_Model_FINAL.xlsx
@@ -82,12 +82,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -135,21 +135,21 @@
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -686,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1083,48 +1083,48 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>FL-&gt;MI cost-of-living [CONFIRM]</t>
+          <t>FL-&gt;MI cost-of-living [Robert to set]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>feedstock</t>
+          <t>xtrain</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Net feedstock cost (negative if tipping-fee positive)</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>0</v>
+          <t>Cross-training / headcount efficiency factor</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>$/yr</t>
+          <t>x</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>[CONFIRM — tires may carry tipping fees]</t>
+          <t>WasteWerx (V.Tizio 5/27): staffing is WORST-CASE; cross-training reduces it [set &lt;1.0]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>utilities</t>
+          <t>feedstock</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Utilities / energy (net of syngas self-supply)</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>1200000</v>
+          <t>Net feedstock cost (negative if tipping-fee positive)</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>0</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1133,23 +1133,23 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>ESTIMATE [CONFIRM]</t>
+          <t>[CONFIRM — tires may carry tipping fees]</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>maint</t>
+          <t>utilities</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Maintenance materials + contract maintenance</t>
+          <t>Utilities / energy (net of syngas self-supply)</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>500000</v>
+        <v>1200000</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -1165,16 +1165,16 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>maint</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Insurance (industrial)</t>
+          <t>Maintenance materials + contract maintenance</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>400000</v>
+        <v>500000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1190,16 +1190,16 @@
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>contracted</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Contracted svcs (security/janitorial/IT/3rd-party MRV verification)</t>
+          <t>Insurance (industrial)</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>350000</v>
+        <v>400000</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1208,23 +1208,23 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>NOT in staffing pro forma — budget separately [CONFIRM]</t>
+          <t>ESTIMATE [CONFIRM]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>ga</t>
+          <t>contracted</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>G&amp;A / SG&amp;A (corporate alloc, legal, accounting, software)</t>
+          <t>Contracted svcs (security/janitorial/IT/3rd-party MRV verification)</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>750000</v>
+        <v>350000</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1233,48 +1233,48 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>ESTIMATE [CONFIRM]</t>
+          <t>NOT in staffing pro forma — budget separately [CONFIRM]</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>raise_site</t>
+          <t>ga</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Project raise per site</t>
+          <t>G&amp;A / SG&amp;A (corporate alloc, legal, accounting, software)</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>15000000</v>
+        <v>750000</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>sponsor-directed headline</t>
+          <t>ESTIMATE [CONFIRM]</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>raise_site</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Use of funds: build / core plant</t>
+          <t>Project raise per site</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>8000000</v>
+        <v>15000000</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1283,23 +1283,23 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>rough verbal</t>
+          <t>sponsor-directed headline</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>addl</t>
+          <t>build</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Use of funds: added construction</t>
+          <t>Use of funds: build / core plant</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>1000000</v>
+        <v>8000000</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1315,16 +1315,16 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>preproc</t>
+          <t>addl</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Use of funds: pre-processing/pre-treatment equip</t>
+          <t>Use of funds: added construction</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1340,16 +1340,16 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>conting</t>
+          <t>preproc</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Use of funds: contingency/fees/payroll/training</t>
+          <t>Use of funds: pre-processing/pre-treatment equip</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>5000000</v>
+        <v>2000000</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1365,16 +1365,16 @@
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>ww_license</t>
+          <t>conting</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>WasteWerx license fee (Yr1, net of design credit)</t>
+          <t>Use of funds: contingency/fees/payroll/training</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>5450000</v>
+        <v>5000000</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1383,23 +1383,23 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>signed Model 3</t>
+          <t>rough verbal</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>ww_design</t>
+          <t>ww_license</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>WasteWerx design fee (credited)</t>
+          <t>WasteWerx license fee (Yr1, net of design credit)</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>50000</v>
+        <v>5450000</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1415,16 +1415,16 @@
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>ww_monitor</t>
+          <t>ww_design</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>WasteWerx Yr1 monitoring fees</t>
+          <t>WasteWerx design fee (credited)</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>175000</v>
+        <v>50000</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>ww_royalty</t>
+          <t>ww_monitor</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>WasteWerx Yr1 production royalty</t>
+          <t>WasteWerx Yr1 monitoring fees</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>995328</v>
+        <v>175000</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1465,16 +1465,16 @@
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>cust_capex</t>
+          <t>ww_royalty</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Customer-side capex (site/utilities/permits/WC)</t>
+          <t>WasteWerx Yr1 production royalty</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>952500</v>
+        <v>995328</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1490,16 +1490,16 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>company_raise</t>
+          <t>cust_capex</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Company-level raise (separate)</t>
+          <t>Customer-side capex (site/utilities/permits/WC)</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>2500000</v>
+        <v>952500</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1508,30 +1508,55 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>sponsor-directed</t>
+          <t>signed Model 3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
+          <t>company_raise</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Company-level raise (separate)</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>sponsor-directed</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
           <t>sites</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Number of sites in network</t>
         </is>
       </c>
-      <c r="C36" s="6" t="n">
+      <c r="C37" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Michigan corridor</t>
         </is>
@@ -1548,7 +1573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -1590,16 +1615,16 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Site labor — loaded, 62 FTE (MI-adjusted)</t>
+          <t>Site labor — loaded (62 FTE worst-case x MI-adj x cross-training)</t>
         </is>
       </c>
       <c r="B5" s="10">
-        <f>Inputs!$C$17*Inputs!$C$18</f>
+        <f>Inputs!$C$17*Inputs!$C$18*Inputs!$C$19</f>
         <v/>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>KNOWN — WasteWerx staffing pro forma</t>
+          <t>WORST-CASE per WasteWerx (V.Tizio); benefits/MI rates need actuals [Robert]</t>
         </is>
       </c>
     </row>
@@ -1609,8 +1634,8 @@
           <t>WasteWerx production royalty (recurring)</t>
         </is>
       </c>
-      <c r="B6" s="10">
-        <f>Inputs!$C$33</f>
+      <c r="B6" s="11">
+        <f>Inputs!$C$34</f>
         <v/>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -1625,8 +1650,8 @@
           <t>WasteWerx monitoring fees (recurring)</t>
         </is>
       </c>
-      <c r="B7" s="10">
-        <f>Inputs!$C$32</f>
+      <c r="B7" s="11">
+        <f>Inputs!$C$33</f>
         <v/>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -1641,8 +1666,8 @@
           <t>Net feedstock cost</t>
         </is>
       </c>
-      <c r="B8" s="11">
-        <f>Inputs!$C$19</f>
+      <c r="B8" s="10">
+        <f>Inputs!$C$20</f>
         <v/>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -1657,8 +1682,8 @@
           <t>Utilities / energy (net of syngas self-supply)</t>
         </is>
       </c>
-      <c r="B9" s="11">
-        <f>Inputs!$C$20</f>
+      <c r="B9" s="10">
+        <f>Inputs!$C$21</f>
         <v/>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -1673,8 +1698,8 @@
           <t>Maintenance materials + contract maintenance</t>
         </is>
       </c>
-      <c r="B10" s="11">
-        <f>Inputs!$C$21</f>
+      <c r="B10" s="10">
+        <f>Inputs!$C$22</f>
         <v/>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -1689,8 +1714,8 @@
           <t>Insurance (industrial)</t>
         </is>
       </c>
-      <c r="B11" s="11">
-        <f>Inputs!$C$22</f>
+      <c r="B11" s="10">
+        <f>Inputs!$C$23</f>
         <v/>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -1705,8 +1730,8 @@
           <t>Contracted services (security/janitorial/IT/3rd-party MRV)</t>
         </is>
       </c>
-      <c r="B12" s="11">
-        <f>Inputs!$C$23</f>
+      <c r="B12" s="10">
+        <f>Inputs!$C$24</f>
         <v/>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -1721,8 +1746,8 @@
           <t>G&amp;A / SG&amp;A</t>
         </is>
       </c>
-      <c r="B13" s="11">
-        <f>Inputs!$C$24</f>
+      <c r="B13" s="10">
+        <f>Inputs!$C$25</f>
         <v/>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -1766,18 +1791,32 @@
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
-          <t>Labor ALONE (MI-adjusted)</t>
+          <t>Labor ALONE (MI-adj x cross-training)</t>
         </is>
       </c>
       <c r="B19" s="17">
-        <f>Inputs!$C$17*Inputs!$C$18</f>
+        <f>Inputs!$C$17*Inputs!$C$18*Inputs!$C$19</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="inlineStr">
         <is>
-          <t>-&gt; exceeds the signed model's entire implied opex above. Signed EBITDA overstates margin.</t>
+          <t>-&gt; at worst-case staffing, labor alone exceeds the signed model's entire implied opex. Signed EBITDA overstates margin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>WasteWerx (V. Tizio, 5/27/26): staffing is intentional worst-case 'overkill'; cross-trained roles will reduce headcount;</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>health insurance &amp; benefits need actuals; salaries are FL market — Robert to adjust to Michigan pay rates. Flex via xtrain + mi_adj inputs.</t>
         </is>
       </c>
     </row>
@@ -1844,7 +1883,7 @@
           <t>Pyrolysis oil — raw, market price</t>
         </is>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="11">
         <f>(Inputs!$C$5*Inputs!$C$6*Inputs!$C$7)*Inputs!$C$9</f>
         <v/>
       </c>
@@ -1865,7 +1904,7 @@
           <t>Carbon black</t>
         </is>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="11">
         <f>(Inputs!$C$5*Inputs!$C$6*Inputs!$C$8)*Inputs!$C$10</f>
         <v/>
       </c>
@@ -1886,7 +1925,7 @@
           <t>Renewable diesel (upgraded fuel)</t>
         </is>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="11">
         <f>Inputs!$C$11</f>
         <v/>
       </c>
@@ -1907,7 +1946,7 @@
           <t>SAF / kerosene (upgraded fuel)</t>
         </is>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="11">
         <f>Inputs!$C$12</f>
         <v/>
       </c>
@@ -1928,7 +1967,7 @@
           <t>D4 RIN</t>
         </is>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="10">
         <f>Inputs!$C$13</f>
         <v/>
       </c>
@@ -1949,7 +1988,7 @@
           <t>D7 RIN</t>
         </is>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="10">
         <f>Inputs!$C$14</f>
         <v/>
       </c>
@@ -1970,7 +2009,7 @@
           <t>Section 45Z — RD</t>
         </is>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="10">
         <f>Inputs!$C$15</f>
         <v/>
       </c>
@@ -1991,7 +2030,7 @@
           <t>Section 45Z — SAF</t>
         </is>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="10">
         <f>Inputs!$C$16</f>
         <v/>
       </c>
@@ -2166,7 +2205,7 @@
         </is>
       </c>
       <c r="B24" s="15">
-        <f>Inputs!$C$25</f>
+        <f>Inputs!$C$26</f>
         <v/>
       </c>
     </row>
@@ -2177,7 +2216,7 @@
         </is>
       </c>
       <c r="B25" s="15">
-        <f>Inputs!$C$30+Inputs!$C$31+Inputs!$C$32+Inputs!$C$33</f>
+        <f>Inputs!$C$31+Inputs!$C$32+Inputs!$C$33+Inputs!$C$34</f>
         <v/>
       </c>
     </row>
@@ -2188,7 +2227,7 @@
         </is>
       </c>
       <c r="B26" s="15">
-        <f>Inputs!$C$34</f>
+        <f>Inputs!$C$35</f>
         <v/>
       </c>
     </row>
@@ -2228,7 +2267,7 @@
         </is>
       </c>
       <c r="B31" s="15">
-        <f>Inputs!$C$26+Inputs!$C$27+Inputs!$C$28+Inputs!$C$29</f>
+        <f>Inputs!$C$27+Inputs!$C$28+Inputs!$C$29+Inputs!$C$30</f>
         <v/>
       </c>
     </row>
@@ -2239,7 +2278,7 @@
         </is>
       </c>
       <c r="B32" s="23">
-        <f>Inputs!$C$25-B31</f>
+        <f>Inputs!$C$26-B31</f>
         <v/>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2321,7 +2360,7 @@
         <v/>
       </c>
       <c r="C5" s="19">
-        <f>Inputs!$C$36</f>
+        <f>Inputs!$C$37</f>
         <v/>
       </c>
       <c r="D5" s="21">
@@ -2345,7 +2384,7 @@
         <v/>
       </c>
       <c r="C6" s="19">
-        <f>Inputs!$C$36</f>
+        <f>Inputs!$C$37</f>
         <v/>
       </c>
       <c r="D6" s="21">
@@ -2369,7 +2408,7 @@
         <v/>
       </c>
       <c r="C7" s="19">
-        <f>Inputs!$C$36</f>
+        <f>Inputs!$C$37</f>
         <v/>
       </c>
       <c r="D7" s="22">
@@ -2393,7 +2432,7 @@
         <v/>
       </c>
       <c r="C8" s="19">
-        <f>Inputs!$C$36</f>
+        <f>Inputs!$C$37</f>
         <v/>
       </c>
       <c r="D8" s="22">
@@ -2417,7 +2456,7 @@
         <v/>
       </c>
       <c r="C9" s="19">
-        <f>Inputs!$C$36</f>
+        <f>Inputs!$C$37</f>
         <v/>
       </c>
       <c r="D9" s="22">
@@ -2441,7 +2480,7 @@
         <v/>
       </c>
       <c r="C10" s="19">
-        <f>Inputs!$C$36</f>
+        <f>Inputs!$C$37</f>
         <v/>
       </c>
       <c r="D10" s="21">
@@ -2465,7 +2504,7 @@
         <v/>
       </c>
       <c r="C11" s="19">
-        <f>Inputs!$C$36</f>
+        <f>Inputs!$C$37</f>
         <v/>
       </c>
       <c r="D11" s="21">
@@ -2535,7 +2574,7 @@
         </is>
       </c>
       <c r="B5" s="25">
-        <f>Inputs!$C$25</f>
+        <f>Inputs!$C$26</f>
         <v/>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -2551,7 +2590,7 @@
         </is>
       </c>
       <c r="B6" s="25">
-        <f>Inputs!$C$25*Inputs!$C$36</f>
+        <f>Inputs!$C$26*Inputs!$C$37</f>
         <v/>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -2567,7 +2606,7 @@
         </is>
       </c>
       <c r="B7" s="25">
-        <f>Inputs!$C$35</f>
+        <f>Inputs!$C$36</f>
         <v/>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -2583,7 +2622,7 @@
         </is>
       </c>
       <c r="B8" s="25">
-        <f>Inputs!$C$25*Inputs!$C$36+Inputs!$C$35</f>
+        <f>Inputs!$C$26*Inputs!$C$37+Inputs!$C$36</f>
         <v/>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -2603,7 +2642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="116" customWidth="1" min="1" max="1"/>
@@ -2713,91 +2752,105 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    staffing pro forma and must be budgeted separately. Labor figure is FL market; add 5-10% for Michigan.</t>
+          <t xml:space="preserve">    staffing pro forma and must be budgeted separately. Labor is intentional WORST-CASE per WasteWerx (V. Tizio,</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    5/27/26): cross-training reduces headcount (set xtrain&lt;1.0), salaries are FL market (set mi_adj for Michigan),</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    and health-insurance/benefits actuals are still pending — net labor could move down (cross-training) or up (MI+benefits).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>CAPITAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * Sponsor use-of-funds (~$16M) exceeds the $15M/site raise by ~$1M — confirm which line absorbs it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * $2.5M company raise stays separate from site SPV totals.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  * Sponsor use-of-funds (~$16M) exceeds the $15M/site raise by ~$1M — confirm which line absorbs it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * $2.5M company raise stays separate from site SPV totals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  * WasteWerx is a LICENSE, not a sale; title stays with WasteWerx; license fee depreciation differs; transfer/termination terms matter.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>GOVERNANCE / LEGAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * Securities: not an offer; securities counsel review required before any circulation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * PublicLogic = governance/document partner, NOT placement agent/broker-dealer; fee FIXED &amp; NON-CONTINGENT.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Community-benefit %: source files say 10%; sponsor flags a conflict — do not publish a number until reconciled.</t>
+          <t xml:space="preserve">  * Securities: not an offer; securities counsel review required before any circulation.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Final site list (Coldwater Phase 2 vs Lincoln) [CONFIRM]; parent-holdco legal name [CONFIRM].</t>
+          <t xml:space="preserve">  * PublicLogic = governance/document partner, NOT placement agent/broker-dealer; fee FIXED &amp; NON-CONTINGENT.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * National Salvage: 'largest treated-wood recycler in the U.S.' unless stronger evidence (a verbal 'in the world' is unverified).</t>
+          <t xml:space="preserve">  * Community-benefit %: source files say 10%; sponsor flags a conflict — do not publish a number until reconciled.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Final site list (Coldwater Phase 2 vs Lincoln) [CONFIRM]; parent-holdco legal name [CONFIRM].</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * National Salvage: 'largest treated-wood recycler in the U.S.' unless stronger evidence (a verbal 'in the world' is unverified).</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Not financial, accounting, securities, or tax advice. Figures trace to the canonical workbook / signed pro forma; verify before use.</t>
         </is>

--- a/docs/business/MichiganLTC_Network_Financial_Model_FINAL.xlsx
+++ b/docs/business/MichiganLTC_Network_Financial_Model_FINAL.xlsx
@@ -82,12 +82,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -135,21 +135,21 @@
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -686,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1120,11 +1120,11 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Net feedstock cost (negative if tipping-fee positive)</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>0</v>
+          <t>Feedstock cost (tires) — co-location may reduce</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="n">
+        <v>3720000</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1133,98 +1133,98 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>[CONFIRM — tires may carry tipping fees]</t>
+          <t>deck Operating Savings tab; co-loc w/ ERR/Geocycle may cut this — BIGGEST swing</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>utilities</t>
+          <t>royalty_gal</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Utilities / energy (net of syngas self-supply)</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>1200000</v>
+          <t>WasteWerx production royalty rate</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="n">
+        <v>0.6</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>$/yr</t>
+          <t>$/gal</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>ESTIMATE [CONFIRM]</t>
+          <t>WasteWerx Model 3 (executed)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>maint</t>
+          <t>annual_gal</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Maintenance materials + contract maintenance</t>
+          <t>Annual fuel output (85% util)</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>500000</v>
+        <v>4467600</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>$/yr</t>
+          <t>gal/yr</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>ESTIMATE [CONFIRM]</t>
+          <t>WasteWerx Model 3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>monitor_mo</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Insurance (industrial)</t>
+          <t>WasteWerx monitoring fee</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>400000</v>
+        <v>35000</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>$/yr</t>
+          <t>$/mo</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>ESTIMATE [CONFIRM]</t>
+          <t>WasteWerx Model 3 (CPI-indexed)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>contracted</t>
+          <t>utilities</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Contracted svcs (security/janitorial/IT/3rd-party MRV verification)</t>
+          <t>Utilities (electric+water+fees)</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>350000</v>
+        <v>96960</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1233,23 +1233,23 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>NOT in staffing pro forma — budget separately [CONFIRM]</t>
+          <t>deck Operating Savings tab</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>ga</t>
+          <t>maint</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>G&amp;A / SG&amp;A (corporate alloc, legal, accounting, software)</t>
+          <t>Maintenance + parts</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>750000</v>
+        <v>42000</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1258,148 +1258,148 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>ESTIMATE [CONFIRM]</t>
+          <t>deck Operating Savings tab [low for plant scale — confirm]</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>raise_site</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Project raise per site</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>15000000</v>
+        <v>78000</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>sponsor-directed headline</t>
+          <t>deck Operating Savings tab</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>property_tax</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Use of funds: build / core plant</t>
+          <t>Property tax</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>8000000</v>
+        <v>168000</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>rough verbal</t>
+          <t>deck Operating Savings tab</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>addl</t>
+          <t>security</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Use of funds: added construction</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>1000000</v>
+        <v>360000</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>rough verbal</t>
+          <t>deck Operating Savings tab</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>preproc</t>
+          <t>legal_acct</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Use of funds: pre-processing/pre-treatment equip</t>
+          <t>Legal + accounting (with PublicLogic)</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>2000000</v>
+        <v>750000</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>rough verbal</t>
+          <t>deck Operating Savings tab (revised)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>conting</t>
+          <t>pl_gov</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Use of funds: contingency/fees/payroll/training</t>
+          <t>PublicLogic governance retainer</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>5000000</v>
+        <v>120000</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>rough verbal</t>
+          <t>deck ($10k/mo)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>ww_license</t>
+          <t>raise_site</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>WasteWerx license fee (Yr1, net of design credit)</t>
+          <t>Project raise per site</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>5450000</v>
+        <v>15000000</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1408,23 +1408,23 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>signed Model 3</t>
+          <t>sponsor-directed headline</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>ww_design</t>
+          <t>build</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>WasteWerx design fee (credited)</t>
+          <t>Use of funds: build / core plant</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>50000</v>
+        <v>8000000</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1433,23 +1433,23 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>signed Model 3</t>
+          <t>rough verbal</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>ww_monitor</t>
+          <t>addl</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>WasteWerx Yr1 monitoring fees</t>
+          <t>Use of funds: added construction</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>175000</v>
+        <v>1000000</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1458,23 +1458,23 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>signed Model 3</t>
+          <t>rough verbal</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>ww_royalty</t>
+          <t>preproc</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>WasteWerx Yr1 production royalty</t>
+          <t>Use of funds: pre-processing/pre-treatment equip</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>995328</v>
+        <v>2000000</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1483,23 +1483,23 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>signed Model 3</t>
+          <t>rough verbal</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>cust_capex</t>
+          <t>conting</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Customer-side capex (site/utilities/permits/WC)</t>
+          <t>Use of funds: contingency/fees/payroll/training</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>952500</v>
+        <v>5000000</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1508,23 +1508,23 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>signed Model 3</t>
+          <t>rough verbal</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>company_raise</t>
+          <t>ww_license</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Company-level raise (separate)</t>
+          <t>WasteWerx license fee (Yr1, net of design credit)</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>2500000</v>
+        <v>5450000</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1533,30 +1533,155 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>sponsor-directed</t>
+          <t>signed Model 3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
+          <t>ww_design</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>WasteWerx design fee (credited)</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>50000</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>signed Model 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>ww_monitor</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>WasteWerx Yr1 monitoring fees</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>175000</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>signed Model 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>ww_royalty</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>WasteWerx Yr1 production royalty</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="n">
+        <v>995328</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>signed Model 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>cust_capex</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Customer-side capex (site/utilities/permits/WC)</t>
+        </is>
+      </c>
+      <c r="C40" s="8" t="n">
+        <v>952500</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>signed Model 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>company_raise</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Company-level raise (separate)</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>$</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>sponsor-directed</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
           <t>sites</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Number of sites in network</t>
         </is>
       </c>
-      <c r="C37" s="6" t="n">
+      <c r="C42" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D42" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Michigan corridor</t>
         </is>
@@ -1573,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -1631,190 +1756,222 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>WasteWerx production royalty (recurring)</t>
-        </is>
-      </c>
-      <c r="B6" s="11">
-        <f>Inputs!$C$34</f>
+          <t>WasteWerx royalty (steady-state, $0.60/gal x output)</t>
+        </is>
+      </c>
+      <c r="B6" s="10">
+        <f>Inputs!$C$21*Inputs!$C$22</f>
         <v/>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>KNOWN — signed model</t>
+          <t>WasteWerx Model 3 — capital-bridge uses Yr1 partial</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>WasteWerx monitoring fees (recurring)</t>
-        </is>
-      </c>
-      <c r="B7" s="11">
-        <f>Inputs!$C$33</f>
+          <t>WasteWerx monitoring ($35k/mo x 12)</t>
+        </is>
+      </c>
+      <c r="B7" s="10">
+        <f>Inputs!$C$23*12</f>
         <v/>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>KNOWN — signed model</t>
+          <t>WasteWerx Model 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Net feedstock cost</t>
-        </is>
-      </c>
-      <c r="B8" s="10">
+          <t>Feedstock cost (tires)</t>
+        </is>
+      </c>
+      <c r="B8" s="11">
         <f>Inputs!$C$20</f>
         <v/>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>[CONFIRM — may be tipping-fee positive]</t>
+          <t>deck; co-loc w/ ERR/Geocycle may reduce — BIGGEST swing</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Utilities / energy (net of syngas self-supply)</t>
+          <t>Utilities (electric+water+fees)</t>
         </is>
       </c>
       <c r="B9" s="10">
-        <f>Inputs!$C$21</f>
+        <f>Inputs!$C$24</f>
         <v/>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>ESTIMATE [CONFIRM]</t>
+          <t>deck Operating Savings tab</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Maintenance materials + contract maintenance</t>
+          <t>Maintenance + parts</t>
         </is>
       </c>
       <c r="B10" s="10">
-        <f>Inputs!$C$22</f>
+        <f>Inputs!$C$25</f>
         <v/>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>ESTIMATE [CONFIRM]</t>
+          <t>deck [low for scale — confirm]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Insurance (industrial)</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="B11" s="10">
-        <f>Inputs!$C$23</f>
+        <f>Inputs!$C$26</f>
         <v/>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>ESTIMATE [CONFIRM]</t>
+          <t>deck Operating Savings tab</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Contracted services (security/janitorial/IT/3rd-party MRV)</t>
+          <t>Property tax</t>
         </is>
       </c>
       <c r="B12" s="10">
-        <f>Inputs!$C$24</f>
+        <f>Inputs!$C$27</f>
         <v/>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>NOT in staffing pro forma [CONFIRM]</t>
+          <t>deck Operating Savings tab</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>G&amp;A / SG&amp;A</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="B13" s="10">
-        <f>Inputs!$C$25</f>
+        <f>Inputs!$C$28</f>
         <v/>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>ESTIMATE [CONFIRM]</t>
+          <t>deck Operating Savings tab</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Legal + accounting (with PublicLogic)</t>
+        </is>
+      </c>
+      <c r="B14" s="10">
+        <f>Inputs!$C$29</f>
+        <v/>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>deck Operating Savings tab (revised)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>PublicLogic governance retainer</t>
+        </is>
+      </c>
+      <c r="B15" s="10">
+        <f>Inputs!$C$30</f>
+        <v/>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>deck ($10k/mo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>TOTAL ANNUAL OPEX (bottom-up)</t>
         </is>
       </c>
-      <c r="B14" s="13">
-        <f>SUM(B5:B13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="B16" s="13">
+        <f>SUM(B5:B15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
         <is>
           <t>Signed model's IMPLIED opex (rev - EBITDA)</t>
         </is>
       </c>
-      <c r="B16" s="15" t="n">
+      <c r="B18" s="15" t="n">
         <v>5381149</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Understatement baked into signed EBITDA (bottom-up - implied)</t>
-        </is>
-      </c>
-      <c r="B17" s="16">
-        <f>B14-B16</f>
-        <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="12" t="inlineStr">
         <is>
+          <t>Understatement baked into signed EBITDA (bottom-up - implied)</t>
+        </is>
+      </c>
+      <c r="B19" s="16">
+        <f>B16-B18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
           <t>Labor ALONE (MI-adj x cross-training)</t>
         </is>
       </c>
-      <c r="B19" s="17">
+      <c r="B21" s="17">
         <f>Inputs!$C$17*Inputs!$C$18*Inputs!$C$19</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>-&gt; at worst-case staffing, labor alone exceeds the signed model's entire implied opex. Signed EBITDA overstates margin.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>WasteWerx (V. Tizio, 5/27/26): staffing is intentional worst-case 'overkill'; cross-trained roles will reduce headcount;</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>health insurance &amp; benefits need actuals; salaries are FL market — Robert to adjust to Michigan pay rates. Flex via xtrain + mi_adj inputs.</t>
         </is>
@@ -1883,7 +2040,7 @@
           <t>Pyrolysis oil — raw, market price</t>
         </is>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="10">
         <f>(Inputs!$C$5*Inputs!$C$6*Inputs!$C$7)*Inputs!$C$9</f>
         <v/>
       </c>
@@ -1904,7 +2061,7 @@
           <t>Carbon black</t>
         </is>
       </c>
-      <c r="B6" s="11">
+      <c r="B6" s="10">
         <f>(Inputs!$C$5*Inputs!$C$6*Inputs!$C$8)*Inputs!$C$10</f>
         <v/>
       </c>
@@ -1915,7 +2072,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Real saleable product; excluded from signed model [CONFIRM price/offtake]</t>
+          <t>CONFLICT: $0 in executed WasteWerx model (Disc.#14); deck-era $750/MT; needs offtake</t>
         </is>
       </c>
     </row>
@@ -1925,7 +2082,7 @@
           <t>Renewable diesel (upgraded fuel)</t>
         </is>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="10">
         <f>Inputs!$C$11</f>
         <v/>
       </c>
@@ -1936,7 +2093,7 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Requires distillation refinery + offtake MOU</t>
+          <t>Split NOT in canonical workbook (blended $35.58M only); needs WasteWerx Model 3 + offtake</t>
         </is>
       </c>
     </row>
@@ -1946,7 +2103,7 @@
           <t>SAF / kerosene (upgraded fuel)</t>
         </is>
       </c>
-      <c r="B8" s="11">
+      <c r="B8" s="10">
         <f>Inputs!$C$12</f>
         <v/>
       </c>
@@ -1957,7 +2114,7 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Requires distillation + offtake; [CONFIRM classification]</t>
+          <t>Split unsourced (blended line only); [CONFIRM classification + offtake]</t>
         </is>
       </c>
     </row>
@@ -1967,7 +2124,7 @@
           <t>D4 RIN</t>
         </is>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="11">
         <f>Inputs!$C$13</f>
         <v/>
       </c>
@@ -1978,7 +2135,7 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>RFS pathway registration required — NOT secured</t>
+          <t>Split unsourced + contingent: RFS registration required (Disc.#16) — NOT secured</t>
         </is>
       </c>
     </row>
@@ -1988,7 +2145,7 @@
           <t>D7 RIN</t>
         </is>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="11">
         <f>Inputs!$C$14</f>
         <v/>
       </c>
@@ -1999,7 +2156,7 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>RFS pathway registration required — NOT secured</t>
+          <t>Split unsourced + contingent: RFS registration required — NOT secured</t>
         </is>
       </c>
     </row>
@@ -2009,7 +2166,7 @@
           <t>Section 45Z — RD</t>
         </is>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="11">
         <f>Inputs!$C$15</f>
         <v/>
       </c>
@@ -2020,7 +2177,7 @@
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>Eligibility + tax counsel required — NOT secured</t>
+          <t>Split unsourced + contingent: 45Z qualification + tax counsel — NOT secured</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2187,7 @@
           <t>Section 45Z — SAF</t>
         </is>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="11">
         <f>Inputs!$C$16</f>
         <v/>
       </c>
@@ -2041,7 +2198,7 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>Eligibility + tax counsel required — NOT secured</t>
+          <t>Split unsourced + contingent: 45Z qualification + tax counsel — NOT secured</t>
         </is>
       </c>
     </row>
@@ -2090,7 +2247,7 @@
         <v/>
       </c>
       <c r="C16" s="20">
-        <f>Opex_BuildUp!$B$14</f>
+        <f>Opex_BuildUp!$B$16</f>
         <v/>
       </c>
       <c r="D16" s="21">
@@ -2114,7 +2271,7 @@
         <v/>
       </c>
       <c r="C17" s="20">
-        <f>Opex_BuildUp!$B$14</f>
+        <f>Opex_BuildUp!$B$16</f>
         <v/>
       </c>
       <c r="D17" s="21">
@@ -2138,7 +2295,7 @@
         <v/>
       </c>
       <c r="C18" s="20">
-        <f>Opex_BuildUp!$B$14</f>
+        <f>Opex_BuildUp!$B$16</f>
         <v/>
       </c>
       <c r="D18" s="22">
@@ -2162,7 +2319,7 @@
         <v/>
       </c>
       <c r="C19" s="20">
-        <f>Opex_BuildUp!$B$14</f>
+        <f>Opex_BuildUp!$B$16</f>
         <v/>
       </c>
       <c r="D19" s="22">
@@ -2205,7 +2362,7 @@
         </is>
       </c>
       <c r="B24" s="15">
-        <f>Inputs!$C$26</f>
+        <f>Inputs!$C$31</f>
         <v/>
       </c>
     </row>
@@ -2216,7 +2373,7 @@
         </is>
       </c>
       <c r="B25" s="15">
-        <f>Inputs!$C$31+Inputs!$C$32+Inputs!$C$33+Inputs!$C$34</f>
+        <f>Inputs!$C$36+Inputs!$C$37+Inputs!$C$38+Inputs!$C$39</f>
         <v/>
       </c>
     </row>
@@ -2227,7 +2384,7 @@
         </is>
       </c>
       <c r="B26" s="15">
-        <f>Inputs!$C$35</f>
+        <f>Inputs!$C$40</f>
         <v/>
       </c>
     </row>
@@ -2267,7 +2424,7 @@
         </is>
       </c>
       <c r="B31" s="15">
-        <f>Inputs!$C$27+Inputs!$C$28+Inputs!$C$29+Inputs!$C$30</f>
+        <f>Inputs!$C$32+Inputs!$C$33+Inputs!$C$34+Inputs!$C$35</f>
         <v/>
       </c>
     </row>
@@ -2278,7 +2435,7 @@
         </is>
       </c>
       <c r="B32" s="23">
-        <f>Inputs!$C$26-B31</f>
+        <f>Inputs!$C$31-B31</f>
         <v/>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2360,7 +2517,7 @@
         <v/>
       </c>
       <c r="C5" s="19">
-        <f>Inputs!$C$37</f>
+        <f>Inputs!$C$42</f>
         <v/>
       </c>
       <c r="D5" s="21">
@@ -2384,7 +2541,7 @@
         <v/>
       </c>
       <c r="C6" s="19">
-        <f>Inputs!$C$37</f>
+        <f>Inputs!$C$42</f>
         <v/>
       </c>
       <c r="D6" s="21">
@@ -2408,7 +2565,7 @@
         <v/>
       </c>
       <c r="C7" s="19">
-        <f>Inputs!$C$37</f>
+        <f>Inputs!$C$42</f>
         <v/>
       </c>
       <c r="D7" s="22">
@@ -2432,7 +2589,7 @@
         <v/>
       </c>
       <c r="C8" s="19">
-        <f>Inputs!$C$37</f>
+        <f>Inputs!$C$42</f>
         <v/>
       </c>
       <c r="D8" s="22">
@@ -2456,7 +2613,7 @@
         <v/>
       </c>
       <c r="C9" s="19">
-        <f>Inputs!$C$37</f>
+        <f>Inputs!$C$42</f>
         <v/>
       </c>
       <c r="D9" s="22">
@@ -2480,7 +2637,7 @@
         <v/>
       </c>
       <c r="C10" s="19">
-        <f>Inputs!$C$37</f>
+        <f>Inputs!$C$42</f>
         <v/>
       </c>
       <c r="D10" s="21">
@@ -2504,7 +2661,7 @@
         <v/>
       </c>
       <c r="C11" s="19">
-        <f>Inputs!$C$37</f>
+        <f>Inputs!$C$42</f>
         <v/>
       </c>
       <c r="D11" s="21">
@@ -2574,7 +2731,7 @@
         </is>
       </c>
       <c r="B5" s="25">
-        <f>Inputs!$C$26</f>
+        <f>Inputs!$C$31</f>
         <v/>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -2590,7 +2747,7 @@
         </is>
       </c>
       <c r="B6" s="25">
-        <f>Inputs!$C$26*Inputs!$C$37</f>
+        <f>Inputs!$C$31*Inputs!$C$42</f>
         <v/>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -2606,7 +2763,7 @@
         </is>
       </c>
       <c r="B7" s="25">
-        <f>Inputs!$C$36</f>
+        <f>Inputs!$C$41</f>
         <v/>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -2622,7 +2779,7 @@
         </is>
       </c>
       <c r="B8" s="25">
-        <f>Inputs!$C$26*Inputs!$C$37+Inputs!$C$36</f>
+        <f>Inputs!$C$31*Inputs!$C$42+Inputs!$C$41</f>
         <v/>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -2642,7 +2799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="116" customWidth="1" min="1" max="1"/>
@@ -2724,133 +2881,140 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * OPEX IS UNDERSTATED IN THE SIGNED MODEL. The uploaded WasteWerx staffing pro forma shows 62 FTE / $5.52M loaded</t>
+          <t xml:space="preserve">  * OPEX IS NOW SOURCED (bottom-up ~$14.2M/site) from the WasteWerx staffing pro forma + deck Operating Savings tab +</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    labor alone — more than the signed model's entire implied opex ($5.38M). Bottom-up opex (Opex_BuildUp sheet) is</t>
+          <t xml:space="preserve">    WasteWerx Model 3 terms — vs the signed model's implied $5.38M. Understatement ~$8.85M.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    materially higher; utilities/maintenance/insurance/contracted/G&amp;A are estimates [CONFIRM with WasteWerx].</t>
+          <t xml:space="preserve">  * Royalty corrected to STEADY-STATE: $0.60/gal x 4,467,600 gal = ~$2.68M/yr ($995k in the capital bridge is Yr1 partial). Monitoring $420k/yr.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Contracted services (security, janitorial, IT/MSP, certified 3rd-party MRV verification) are explicitly NOT in the</t>
+          <t xml:space="preserve">  * FEEDSTOCK $3.72M (tires, deck) is the BIGGEST swing — co-location with ERR/Geocycle may cut it materially. [CONFIRM]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    staffing pro forma and must be budgeted separately. Labor is intentional WORST-CASE per WasteWerx (V. Tizio,</t>
+          <t xml:space="preserve">  * REVENUE SPLIT NOT IN CANONICAL WORKBOOK: executed pro forma shows only blended 'Fuel+RIN+§45Z' = $35.58M; the RD/SAF/RIN/45Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    5/27/26): cross-training reduces headcount (set xtrain&lt;1.0), salaries are FL market (set mi_adj for Michigan),</t>
+          <t xml:space="preserve">    line items trace to the investor doc, not a source — need the underlying WasteWerx Model 3 to verify the split.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    and health-insurance/benefits actuals are still pending — net labor could move down (cross-training) or up (MI+benefits).</t>
+          <t xml:space="preserve">  * CARBON BLACK = $0 in executed WasteWerx model (Disc.#14) but $10.1M in the deck; base case includes it on the DECK assumption — confirm.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Labor is worst-case (V. Tizio 5/27): set xtrain (cross-training) + mi_adj (Michigan); benefits actuals pending.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>CAPITAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * Sponsor use-of-funds (~$16M) exceeds the $15M/site raise by ~$1M — confirm which line absorbs it.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * $2.5M company raise stays separate from site SPV totals.</t>
+          <t xml:space="preserve">  * Sponsor use-of-funds (~$16M) exceeds the $15M/site raise by ~$1M — confirm which line absorbs it.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  * $2.5M company raise stays separate from site SPV totals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  * WasteWerx is a LICENSE, not a sale; title stays with WasteWerx; license fee depreciation differs; transfer/termination terms matter.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-    </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>GOVERNANCE / LEGAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * Securities: not an offer; securities counsel review required before any circulation.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * PublicLogic = governance/document partner, NOT placement agent/broker-dealer; fee FIXED &amp; NON-CONTINGENT.</t>
+          <t xml:space="preserve">  * Securities: not an offer; securities counsel review required before any circulation.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Community-benefit %: source files say 10%; sponsor flags a conflict — do not publish a number until reconciled.</t>
+          <t xml:space="preserve">  * PublicLogic = governance/document partner, NOT placement agent/broker-dealer; fee FIXED &amp; NON-CONTINGENT.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Final site list (Coldwater Phase 2 vs Lincoln) [CONFIRM]; parent-holdco legal name [CONFIRM].</t>
+          <t xml:space="preserve">  * Community-benefit %: source files say 10%; sponsor flags a conflict — do not publish a number until reconciled.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  * Final site list (Coldwater Phase 2 vs Lincoln) [CONFIRM]; parent-holdco legal name [CONFIRM].</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  * National Salvage: 'largest treated-wood recycler in the U.S.' unless stronger evidence (a verbal 'in the world' is unverified).</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-    </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+      <c r="A33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>Not financial, accounting, securities, or tax advice. Figures trace to the canonical workbook / signed pro forma; verify before use.</t>
         </is>

--- a/docs/business/MichiganLTC_Network_Financial_Model_FINAL.xlsx
+++ b/docs/business/MichiganLTC_Network_Financial_Model_FINAL.xlsx
@@ -686,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -890,16 +890,16 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>rd_rev</t>
+          <t>fuel_base</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Upgraded fuel: Renewable diesel revenue</t>
+          <t>WasteWerx fuel revenue (distilled RD+SAF, base)</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>4798080</v>
+        <v>22181680</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -908,23 +908,23 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>signed Model 3 [requires distillation+offtake]</t>
+          <t>CONFIRMED: $35,581,680 total minus ~$13.4M credits (13_Financial_Reconciliation)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>saf_rev</t>
+          <t>credits</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Upgraded fuel: SAF/kerosene revenue</t>
+          <t>RIN + Section 45Z (CONTINGENT)</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>10355040</v>
+        <v>13400000</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -933,23 +933,23 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>signed Model 3 [CONFIRM product classification]</t>
+          <t>CONFIRMED contingent: '$13.4M+/yr requires EPA RFS registration — NOT guaranteed'</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>d4_rin</t>
+          <t>labor_fl</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>D4 RIN value (CONTINGENT)</t>
+          <t>Site labor — total loaded, 62 FTE (FL basis)</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>4798080</v>
+        <v>5522400</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -958,73 +958,73 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>signed Model 3 [RFS registration required]</t>
+          <t>WasteWerx Staffing Pro Forma (uploaded); FL market</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>d7_rin</t>
+          <t>mi_adj</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>D7 RIN value (CONTINGENT)</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>9204480</v>
+          <t>Michigan labor adjustment factor</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>1.05</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>$/yr</t>
+          <t>x</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>signed Model 3 [RFS registration required]</t>
+          <t>FL-&gt;MI cost-of-living [Robert to set]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>z45_rd</t>
+          <t>xtrain</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Section 45Z value - RD (CONTINGENT)</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>2399040</v>
+          <t>Cross-training / headcount efficiency factor</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>$/yr</t>
+          <t>x</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>signed Model 3 [eligibility + tax counsel]</t>
+          <t>WasteWerx (V.Tizio 5/27): staffing is WORST-CASE; cross-training reduces it [set &lt;1.0]</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>z45_saf</t>
+          <t>feedstock</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Section 45Z value - SAF (CONTINGENT)</t>
+          <t>Feedstock cost (tires) — co-location may reduce</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>4026960</v>
+        <v>3720000</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1033,98 +1033,98 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>signed Model 3 [eligibility + tax counsel]</t>
+          <t>deck Operating Savings tab; co-loc w/ ERR/Geocycle may cut this — BIGGEST swing</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>labor_fl</t>
+          <t>royalty_gal</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Site labor — total loaded, 62 FTE (FL basis)</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>5522400</v>
+          <t>WasteWerx production royalty rate</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>0.6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>$/yr</t>
+          <t>$/gal</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>WasteWerx Staffing Pro Forma (uploaded); FL market</t>
+          <t>WasteWerx Model 3 (executed)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>mi_adj</t>
+          <t>annual_gal</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Michigan labor adjustment factor</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="n">
-        <v>1.05</v>
+          <t>Annual fuel output (85% util)</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="n">
+        <v>4467600</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>gal/yr</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>FL-&gt;MI cost-of-living [Robert to set]</t>
+          <t>WasteWerx Model 3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>xtrain</t>
+          <t>monitor_mo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cross-training / headcount efficiency factor</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>1</v>
+          <t>WasteWerx monitoring fee</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="n">
+        <v>35000</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>$/mo</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>WasteWerx (V.Tizio 5/27): staffing is WORST-CASE; cross-training reduces it [set &lt;1.0]</t>
+          <t>WasteWerx Model 3 (CPI-indexed)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>feedstock</t>
+          <t>utilities</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Feedstock cost (tires) — co-location may reduce</t>
+          <t>Utilities (electric+water+fees)</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>3720000</v>
+        <v>96960</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1133,98 +1133,98 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>deck Operating Savings tab; co-loc w/ ERR/Geocycle may cut this — BIGGEST swing</t>
+          <t>deck Operating Savings tab</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>royalty_gal</t>
+          <t>maint</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>WasteWerx production royalty rate</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="n">
-        <v>0.6</v>
+          <t>Maintenance + parts</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="n">
+        <v>42000</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>$/gal</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>WasteWerx Model 3 (executed)</t>
+          <t>deck Operating Savings tab [low for plant scale — confirm]</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>annual_gal</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Annual fuel output (85% util)</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>4467600</v>
+        <v>78000</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>gal/yr</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>WasteWerx Model 3</t>
+          <t>deck Operating Savings tab</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>monitor_mo</t>
+          <t>property_tax</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>WasteWerx monitoring fee</t>
+          <t>Property tax</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>35000</v>
+        <v>168000</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>$/mo</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>WasteWerx Model 3 (CPI-indexed)</t>
+          <t>deck Operating Savings tab</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>utilities</t>
+          <t>security</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Utilities (electric+water+fees)</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>96960</v>
+        <v>360000</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1240,16 +1240,16 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>maint</t>
+          <t>legal_acct</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Maintenance + parts</t>
+          <t>Legal + accounting (with PublicLogic)</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>42000</v>
+        <v>750000</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1258,23 +1258,23 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>deck Operating Savings tab [low for plant scale — confirm]</t>
+          <t>deck Operating Savings tab (revised)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>pl_gov</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>PublicLogic governance retainer</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>78000</v>
+        <v>120000</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1283,123 +1283,123 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>deck Operating Savings tab</t>
+          <t>deck ($10k/mo)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>property_tax</t>
+          <t>raise_site</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Property tax</t>
+          <t>Project raise per site</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>168000</v>
+        <v>15000000</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>$/yr</t>
+          <t>$</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>deck Operating Savings tab</t>
+          <t>sponsor-directed headline</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>build</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Use of funds: build / core plant</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>360000</v>
+        <v>8000000</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>$/yr</t>
+          <t>$</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>deck Operating Savings tab</t>
+          <t>rough verbal</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>legal_acct</t>
+          <t>addl</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Legal + accounting (with PublicLogic)</t>
+          <t>Use of funds: added construction</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>750000</v>
+        <v>1000000</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>$/yr</t>
+          <t>$</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>deck Operating Savings tab (revised)</t>
+          <t>rough verbal</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>pl_gov</t>
+          <t>preproc</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PublicLogic governance retainer</t>
+          <t>Use of funds: pre-processing/pre-treatment equip</t>
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>120000</v>
+        <v>2000000</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>$/yr</t>
+          <t>$</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>deck ($10k/mo)</t>
+          <t>rough verbal</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>raise_site</t>
+          <t>conting</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Project raise per site</t>
+          <t>Use of funds: contingency/fees/payroll/training</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>15000000</v>
+        <v>5000000</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1408,23 +1408,23 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>sponsor-directed headline</t>
+          <t>rough verbal</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>ww_license</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Use of funds: build / core plant</t>
+          <t>WasteWerx license fee (Yr1, net of design credit)</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>8000000</v>
+        <v>5450000</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1433,23 +1433,23 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>rough verbal</t>
+          <t>signed Model 3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>addl</t>
+          <t>ww_design</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Use of funds: added construction</t>
+          <t>WasteWerx design fee (credited)</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>1000000</v>
+        <v>50000</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1458,23 +1458,23 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>rough verbal</t>
+          <t>signed Model 3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>preproc</t>
+          <t>ww_monitor</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Use of funds: pre-processing/pre-treatment equip</t>
+          <t>WasteWerx Yr1 monitoring fees</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>2000000</v>
+        <v>175000</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1483,23 +1483,23 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>rough verbal</t>
+          <t>signed Model 3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>conting</t>
+          <t>ww_royalty</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Use of funds: contingency/fees/payroll/training</t>
+          <t>WasteWerx Yr1 production royalty</t>
         </is>
       </c>
       <c r="C35" s="8" t="n">
-        <v>5000000</v>
+        <v>995328</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1508,23 +1508,23 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>rough verbal</t>
+          <t>signed Model 3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>ww_license</t>
+          <t>cust_capex</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WasteWerx license fee (Yr1, net of design credit)</t>
+          <t>Customer-side capex (site/utilities/permits/WC)</t>
         </is>
       </c>
       <c r="C36" s="8" t="n">
-        <v>5450000</v>
+        <v>952500</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1540,16 +1540,16 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>ww_design</t>
+          <t>company_raise</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>WasteWerx design fee (credited)</t>
+          <t>Company-level raise (separate)</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>50000</v>
+        <v>2500000</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1558,130 +1558,30 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>signed Model 3</t>
+          <t>sponsor-directed</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>ww_monitor</t>
+          <t>sites</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>WasteWerx Yr1 monitoring fees</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n">
-        <v>175000</v>
+          <t>Number of sites in network</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>signed Model 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>ww_royalty</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>WasteWerx Yr1 production royalty</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="n">
-        <v>995328</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>signed Model 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>cust_capex</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Customer-side capex (site/utilities/permits/WC)</t>
-        </is>
-      </c>
-      <c r="C40" s="8" t="n">
-        <v>952500</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>signed Model 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>company_raise</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Company-level raise (separate)</t>
-        </is>
-      </c>
-      <c r="C41" s="8" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>sponsor-directed</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>sites</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Number of sites in network</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Michigan corridor</t>
         </is>
@@ -1744,7 +1644,7 @@
         </is>
       </c>
       <c r="B5" s="10">
-        <f>Inputs!$C$17*Inputs!$C$18*Inputs!$C$19</f>
+        <f>Inputs!$C$13*Inputs!$C$14*Inputs!$C$15</f>
         <v/>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -1760,7 +1660,7 @@
         </is>
       </c>
       <c r="B6" s="10">
-        <f>Inputs!$C$21*Inputs!$C$22</f>
+        <f>Inputs!$C$17*Inputs!$C$18</f>
         <v/>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -1776,7 +1676,7 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>Inputs!$C$23*12</f>
+        <f>Inputs!$C$19*12</f>
         <v/>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -1792,7 +1692,7 @@
         </is>
       </c>
       <c r="B8" s="11">
-        <f>Inputs!$C$20</f>
+        <f>Inputs!$C$16</f>
         <v/>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -1808,7 +1708,7 @@
         </is>
       </c>
       <c r="B9" s="10">
-        <f>Inputs!$C$24</f>
+        <f>Inputs!$C$20</f>
         <v/>
       </c>
       <c r="C9" s="9" t="inlineStr">
@@ -1824,7 +1724,7 @@
         </is>
       </c>
       <c r="B10" s="10">
-        <f>Inputs!$C$25</f>
+        <f>Inputs!$C$21</f>
         <v/>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -1840,7 +1740,7 @@
         </is>
       </c>
       <c r="B11" s="10">
-        <f>Inputs!$C$26</f>
+        <f>Inputs!$C$22</f>
         <v/>
       </c>
       <c r="C11" s="9" t="inlineStr">
@@ -1856,7 +1756,7 @@
         </is>
       </c>
       <c r="B12" s="10">
-        <f>Inputs!$C$27</f>
+        <f>Inputs!$C$23</f>
         <v/>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -1872,7 +1772,7 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>Inputs!$C$28</f>
+        <f>Inputs!$C$24</f>
         <v/>
       </c>
       <c r="C13" s="9" t="inlineStr">
@@ -1888,7 +1788,7 @@
         </is>
       </c>
       <c r="B14" s="10">
-        <f>Inputs!$C$29</f>
+        <f>Inputs!$C$25</f>
         <v/>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -1904,7 +1804,7 @@
         </is>
       </c>
       <c r="B15" s="10">
-        <f>Inputs!$C$30</f>
+        <f>Inputs!$C$26</f>
         <v/>
       </c>
       <c r="C15" s="9" t="inlineStr">
@@ -1952,7 +1852,7 @@
         </is>
       </c>
       <c r="B21" s="17">
-        <f>Inputs!$C$17*Inputs!$C$18*Inputs!$C$19</f>
+        <f>Inputs!$C$13*Inputs!$C$14*Inputs!$C$15</f>
         <v/>
       </c>
     </row>
@@ -2037,28 +1937,28 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Pyrolysis oil — raw, market price</t>
+          <t>WasteWerx fuel (distilled RD+SAF)</t>
         </is>
       </c>
       <c r="B5" s="10">
-        <f>(Inputs!$C$5*Inputs!$C$6*Inputs!$C$7)*Inputs!$C$9</f>
+        <f>Inputs!$C$11</f>
         <v/>
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>BASE (conservative)</t>
+          <t>BASE</t>
         </is>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Market-grounded; most defensible</t>
+          <t>CONFIRMED: $35.58M total minus ~$13.4M credits (13_Financial_Reconciliation)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Carbon black</t>
+          <t>Carbon black (deck-era; additive?)</t>
         </is>
       </c>
       <c r="B6" s="10">
@@ -2067,138 +1967,33 @@
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>BASE</t>
+          <t>ADD'L (contingent)</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>CONFLICT: $0 in executed WasteWerx model (Disc.#14); deck-era $750/MT; needs offtake</t>
+          <t>$0 in executed WasteWerx pro forma — confirm if additive + offtake before use</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Renewable diesel (upgraded fuel)</t>
-        </is>
-      </c>
-      <c r="B7" s="10">
-        <f>Inputs!$C$11</f>
+          <t>RIN + Section 45Z (credits)</t>
+        </is>
+      </c>
+      <c r="B7" s="11">
+        <f>Inputs!$C$12</f>
         <v/>
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t>BASE (upgraded)</t>
+          <t>CONTINGENT UPSIDE</t>
         </is>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Split NOT in canonical workbook (blended $35.58M only); needs WasteWerx Model 3 + offtake</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>SAF / kerosene (upgraded fuel)</t>
-        </is>
-      </c>
-      <c r="B8" s="10">
-        <f>Inputs!$C$12</f>
-        <v/>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>BASE (upgraded)</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="inlineStr">
-        <is>
-          <t>Split unsourced (blended line only); [CONFIRM classification + offtake]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>D4 RIN</t>
-        </is>
-      </c>
-      <c r="B9" s="11">
-        <f>Inputs!$C$13</f>
-        <v/>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>CONTINGENT UPSIDE</t>
-        </is>
-      </c>
-      <c r="D9" s="9" t="inlineStr">
-        <is>
-          <t>Split unsourced + contingent: RFS registration required (Disc.#16) — NOT secured</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>D7 RIN</t>
-        </is>
-      </c>
-      <c r="B10" s="11">
-        <f>Inputs!$C$14</f>
-        <v/>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>CONTINGENT UPSIDE</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>Split unsourced + contingent: RFS registration required — NOT secured</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Section 45Z — RD</t>
-        </is>
-      </c>
-      <c r="B11" s="11">
-        <f>Inputs!$C$15</f>
-        <v/>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>CONTINGENT UPSIDE</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Split unsourced + contingent: 45Z qualification + tax counsel — NOT secured</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Section 45Z — SAF</t>
-        </is>
-      </c>
-      <c r="B12" s="11">
-        <f>Inputs!$C$16</f>
-        <v/>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>CONTINGENT UPSIDE</t>
-        </is>
-      </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>Split unsourced + contingent: 45Z qualification + tax counsel — NOT secured</t>
+          <t>CONFIRMED contingent: ~$13.4M+; requires EPA RFS registration — NOT guaranteed</t>
         </is>
       </c>
     </row>
@@ -2239,11 +2034,11 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Base — Conservative (raw oil + carbon black)</t>
+          <t>Base — WasteWerx fuel only (no credits, no CB)</t>
         </is>
       </c>
       <c r="B16" s="20">
-        <f>B5+B6</f>
+        <f>B5</f>
         <v/>
       </c>
       <c r="C16" s="20">
@@ -2256,18 +2051,18 @@
       </c>
       <c r="E16" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No — most defensible</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Base — Upgraded (RD + SAF + carbon black)</t>
+          <t>Base + carbon black (if additive)</t>
         </is>
       </c>
       <c r="B17" s="20">
-        <f>B7+B8+B6</f>
+        <f>B5+B6</f>
         <v/>
       </c>
       <c r="C17" s="20">
@@ -2280,18 +2075,18 @@
       </c>
       <c r="E17" s="19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No (CB itself contingent)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Signed headline (RD + SAF + credits, no carbon black)</t>
+          <t>WasteWerx confirmed headline (fuel + credits, no CB)</t>
         </is>
       </c>
       <c r="B18" s="20">
-        <f>B7+B8+B9+B10+B11+B12</f>
+        <f>B5+B7</f>
         <v/>
       </c>
       <c r="C18" s="20">
@@ -2304,18 +2099,18 @@
       </c>
       <c r="E18" s="19" t="inlineStr">
         <is>
-          <t>YES — ~$20.4M credit-dependent</t>
+          <t>YES — ~$13.4M credit-dependent</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Full stack (upgraded fuel + carbon black + credits)</t>
+          <t>Full stack (fuel + carbon black + credits)</t>
         </is>
       </c>
       <c r="B19" s="20">
-        <f>B6+B7+B8+B9+B10+B11+B12</f>
+        <f>B5+B6+B7</f>
         <v/>
       </c>
       <c r="C19" s="20">
@@ -2339,7 +2134,7 @@
         </is>
       </c>
       <c r="B21" s="16">
-        <f>B9+B10+B11+B12</f>
+        <f>B7</f>
         <v/>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2362,7 +2157,7 @@
         </is>
       </c>
       <c r="B24" s="15">
-        <f>Inputs!$C$31</f>
+        <f>Inputs!$C$27</f>
         <v/>
       </c>
     </row>
@@ -2373,7 +2168,7 @@
         </is>
       </c>
       <c r="B25" s="15">
-        <f>Inputs!$C$36+Inputs!$C$37+Inputs!$C$38+Inputs!$C$39</f>
+        <f>Inputs!$C$32+Inputs!$C$33+Inputs!$C$34+Inputs!$C$35</f>
         <v/>
       </c>
     </row>
@@ -2384,7 +2179,7 @@
         </is>
       </c>
       <c r="B26" s="15">
-        <f>Inputs!$C$40</f>
+        <f>Inputs!$C$36</f>
         <v/>
       </c>
     </row>
@@ -2424,7 +2219,7 @@
         </is>
       </c>
       <c r="B31" s="15">
-        <f>Inputs!$C$32+Inputs!$C$33+Inputs!$C$34+Inputs!$C$35</f>
+        <f>Inputs!$C$28+Inputs!$C$29+Inputs!$C$30+Inputs!$C$31</f>
         <v/>
       </c>
     </row>
@@ -2435,7 +2230,7 @@
         </is>
       </c>
       <c r="B32" s="23">
-        <f>Inputs!$C$31-B31</f>
+        <f>Inputs!$C$27-B31</f>
         <v/>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2517,7 +2312,7 @@
         <v/>
       </c>
       <c r="C5" s="19">
-        <f>Inputs!$C$42</f>
+        <f>Inputs!$C$38</f>
         <v/>
       </c>
       <c r="D5" s="21">
@@ -2541,7 +2336,7 @@
         <v/>
       </c>
       <c r="C6" s="19">
-        <f>Inputs!$C$42</f>
+        <f>Inputs!$C$38</f>
         <v/>
       </c>
       <c r="D6" s="21">
@@ -2565,7 +2360,7 @@
         <v/>
       </c>
       <c r="C7" s="19">
-        <f>Inputs!$C$42</f>
+        <f>Inputs!$C$38</f>
         <v/>
       </c>
       <c r="D7" s="22">
@@ -2589,7 +2384,7 @@
         <v/>
       </c>
       <c r="C8" s="19">
-        <f>Inputs!$C$42</f>
+        <f>Inputs!$C$38</f>
         <v/>
       </c>
       <c r="D8" s="22">
@@ -2613,7 +2408,7 @@
         <v/>
       </c>
       <c r="C9" s="19">
-        <f>Inputs!$C$42</f>
+        <f>Inputs!$C$38</f>
         <v/>
       </c>
       <c r="D9" s="22">
@@ -2637,7 +2432,7 @@
         <v/>
       </c>
       <c r="C10" s="19">
-        <f>Inputs!$C$42</f>
+        <f>Inputs!$C$38</f>
         <v/>
       </c>
       <c r="D10" s="21">
@@ -2661,7 +2456,7 @@
         <v/>
       </c>
       <c r="C11" s="19">
-        <f>Inputs!$C$42</f>
+        <f>Inputs!$C$38</f>
         <v/>
       </c>
       <c r="D11" s="21">
@@ -2731,7 +2526,7 @@
         </is>
       </c>
       <c r="B5" s="25">
-        <f>Inputs!$C$31</f>
+        <f>Inputs!$C$27</f>
         <v/>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -2747,7 +2542,7 @@
         </is>
       </c>
       <c r="B6" s="25">
-        <f>Inputs!$C$31*Inputs!$C$42</f>
+        <f>Inputs!$C$27*Inputs!$C$38</f>
         <v/>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -2763,7 +2558,7 @@
         </is>
       </c>
       <c r="B7" s="25">
-        <f>Inputs!$C$41</f>
+        <f>Inputs!$C$37</f>
         <v/>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -2779,7 +2574,7 @@
         </is>
       </c>
       <c r="B8" s="25">
-        <f>Inputs!$C$31*Inputs!$C$42+Inputs!$C$41</f>
+        <f>Inputs!$C$27*Inputs!$C$38+Inputs!$C$37</f>
         <v/>
       </c>
       <c r="C8" s="9" t="inlineStr">
@@ -2799,7 +2594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A34"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="116" customWidth="1" min="1" max="1"/>
@@ -2895,126 +2690,147 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Royalty corrected to STEADY-STATE: $0.60/gal x 4,467,600 gal = ~$2.68M/yr ($995k in the capital bridge is Yr1 partial). Monitoring $420k/yr.</t>
+          <t xml:space="preserve">  * THE $30.2M EBITDA IS WASTEWERX-SCOPE: it sits on WasteWerx's confirmed $5.38M opex (fees + minimal ops) which OMITS the</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * FEEDSTOCK $3.72M (tires, deck) is the BIGGEST swing — co-location with ERR/Geocycle may cut it materially. [CONFIRM]</t>
+          <t xml:space="preserve">    customer's full 62-FTE site labor (~$5.5M) and feedstock (~$1-3.7M). On the customer's all-in opex (~$14.2M) the SAME</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * REVENUE SPLIT NOT IN CANONICAL WORKBOOK: executed pro forma shows only blended 'Fuel+RIN+§45Z' = $35.58M; the RD/SAF/RIN/45Z</t>
+          <t xml:space="preserve">    $35.58M revenue yields ~$21.35M EBITDA, not $30.2M. (The deck's own reconciled model shows ~$11.2M expenses / ~$5.66M net income.)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    line items trace to the investor doc, not a source — need the underlying WasteWerx Model 3 to verify the split.</t>
+          <t xml:space="preserve">  * Royalty corrected to STEADY-STATE: $0.60/gal x 4,467,600 gal = ~$2.68M/yr ($995k in the capital bridge is Yr1 partial). Monitoring $420k/yr.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * CARBON BLACK = $0 in executed WasteWerx model (Disc.#14) but $10.1M in the deck; base case includes it on the DECK assumption — confirm.</t>
+          <t xml:space="preserve">  * FEEDSTOCK is a CONFIRMED swing: deck $200/ton landed = $3.72M vs Dort Hwy agreement $25/ton tipping = ~$1M. Resolve with Robert. [CONFIRM]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Labor is worst-case (V. Tizio 5/27): set xtrain (cross-training) + mi_adj (Michigan); benefits actuals pending.</t>
+          <t xml:space="preserve">  * REVENUE SPLIT NOT IN CANONICAL WORKBOOK: executed pro forma shows only blended 'Fuel+RIN+§45Z' = $35.58M; the RD/SAF/RIN/45Z</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    line items trace to the investor doc, not a source — need the underlying WasteWerx Model 3 to verify the split.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>CAPITAL</t>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * CARBON BLACK = $0 in executed WasteWerx model (Disc.#14) but $10.1M in the deck; base case includes it on the DECK assumption — confirm.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">    Labor is worst-case (V. Tizio 5/27): set xtrain (cross-training) + mi_adj (Michigan); benefits actuals pending.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>CAPITAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  * Sponsor use-of-funds (~$16M) exceeds the $15M/site raise by ~$1M — confirm which line absorbs it.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  * $2.5M company raise stays separate from site SPV totals.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * WasteWerx is a LICENSE, not a sale; title stays with WasteWerx; license fee depreciation differs; transfer/termination terms matter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>GOVERNANCE / LEGAL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Securities: not an offer; securities counsel review required before any circulation.</t>
+          <t xml:space="preserve">  * WasteWerx is a LICENSE, not a sale; title stays with WasteWerx; license fee depreciation differs; transfer/termination terms matter.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * PublicLogic = governance/document partner, NOT placement agent/broker-dealer; fee FIXED &amp; NON-CONTINGENT.</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * Community-benefit %: source files say 10%; sponsor flags a conflict — do not publish a number until reconciled.</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>GOVERNANCE / LEGAL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Final site list (Coldwater Phase 2 vs Lincoln) [CONFIRM]; parent-holdco legal name [CONFIRM].</t>
+          <t xml:space="preserve">  * Securities: not an offer; securities counsel review required before any circulation.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * National Salvage: 'largest treated-wood recycler in the U.S.' unless stronger evidence (a verbal 'in the world' is unverified).</t>
+          <t xml:space="preserve">  * PublicLogic = governance/document partner, NOT placement agent/broker-dealer; fee FIXED &amp; NON-CONTINGENT.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Community-benefit %: source files say 10%; sponsor flags a conflict — do not publish a number until reconciled.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Final site list (Coldwater Phase 2 vs Lincoln) [CONFIRM]; parent-holdco legal name [CONFIRM].</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * National Salvage: 'largest treated-wood recycler in the U.S.' unless stronger evidence (a verbal 'in the world' is unverified).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>Not financial, accounting, securities, or tax advice. Figures trace to the canonical workbook / signed pro forma; verify before use.</t>
         </is>

--- a/docs/business/MichiganLTC_Network_Financial_Model_FINAL.xlsx
+++ b/docs/business/MichiganLTC_Network_Financial_Model_FINAL.xlsx
@@ -9,11 +9,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inputs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opex_BuildUp" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per_Site" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Network" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raises" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Caveats" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Opex" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Corridor" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flags" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -60,10 +61,10 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="007A1F1F"/>
+      <sz val="12"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -88,6 +89,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4C7C3"/>
       </patternFill>
     </fill>
   </fills>
@@ -117,7 +123,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -126,30 +132,29 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="3" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -517,7 +522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="112" customWidth="1" min="1" max="1"/>
@@ -526,14 +531,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Michigan LTC Network — Reconciled Financial Model (FINAL working)</t>
+          <t>Michigan LTC — Financial Model (keyed to Canonical v2.0 / executed Pro Forma)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Base case (fuel + carbon black) anchors the headline; RIN + Section 45Z shown separately as contingent upside. Yellow = editable inputs. Green = defensible base. Orange = contingent. Date 2026-06-03. Not financial/legal/tax advice.</t>
+          <t>Every figure is a signed-document value or a formula over one. Yellow = input. Date 2026-06-03. Not financial/legal advice.</t>
         </is>
       </c>
     </row>
@@ -543,73 +548,73 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>THE RECONCILIATION (why this model)</t>
+          <t>THE CENTRAL FINDING</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">  The signed WasteWerx Model 3 headline (~$35.58M rev / ~$30.2M EBITDA per site) depends on ~$20.4M of</t>
+          <t xml:space="preserve">  The signed $30,200,531 EBITDA is real as a DOCUMENT, but it rests on two things diligence will test:</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  RIN + Section 45Z credits that are NOT secured (registration, eligibility, monetization, counsel/tax review</t>
+          <t xml:space="preserve">   1. OPEX: the Pro Forma opex of $5,381,149 assumes only 4 FTE + 1 manager ($425,000). WasteWerx's OWN staffing</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  all required). This model anchors a DEFENSIBLE base case and shows credits separately as contingent upside.</t>
+          <t xml:space="preserve">      pro forma says the plant needs 62 FTE ($5,522,400). On operator-reality staffing the EBITDA falls to ~$22M.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   2. CREDITS: $20,428,560 of the $35,581,680 revenue is RIN + Section 45Z — contingent on EPA RFS registration</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>HOW TO READ</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      (Flag 3). Base fuel (RD+SAF) is only $15,153,120. Carbon black is $0 in the executed Pro Forma (Flag 1).</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Per_Site  - line-by-line revenue build-up + 4 scenarios (conservative base, upgraded base, signed headline,</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              full stack) with EBITDA each, and the per-site capital bridge.</t>
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>THREE INCOMPATIBLE REVENUE MODELS (reconciled here)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Network   - 3-site rollup.</t>
+          <t xml:space="preserve">  * Investor Brief / EM&amp;S deck: raw oil $6.75M + carbon black $10.125M = $16.875M (credits EXCLUDED as upside).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Raises    - $15M/site project raise + use-of-funds reconciliation; separate $2.5M company raise.</t>
+          <t xml:space="preserve">  * Canonical v2.0 (executed Pro Forma): distilled fuel RD+SAF $15.15M + credits $20.43M = $35.58M (CB EXCLUDED).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Caveats   - what must be confirmed / reviewed before any investor-facing use.</t>
+          <t xml:space="preserve">  * This model uses the Canonical (signed) split and shows the deck's alternative for reference.</t>
         </is>
       </c>
     </row>
@@ -619,59 +624,52 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>THE SAFE INVESTOR HEADLINE</t>
+          <t>HOW TO READ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Lead with BASE EBITDA (no credits). Show RIN/45Z as labeled contingent upside with a footnote. Do NOT make</t>
+          <t xml:space="preserve">  Revenue  - exact RD/SAF/RIN/45Z build-up (Canonical Revenue tab).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  the deck depend on credits that are not secured. This keeps the opportunity big and survives diligence.</t>
+          <t xml:space="preserve">  Opex     - Pro Forma (as signed, 5 FTE) vs Operator-reality (62-FTE staffing + real feedstock). Two cases.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  P&amp;L      - EBITDA matrix: revenue case x opex case. The honest range, not a single number.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>GUARDRAILS</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Corridor - 3-site rollup. Capital - the two raises. Flags - the open commercial items + support letters.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * Carbon black is INCLUDED in this base case as a real saleable product (the signed model excluded it). [CONFIRM price/offtake]</t>
-        </is>
-      </c>
+      <c r="A22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * SAF/kerosene classification, RFS pathway (D4/D7 RIN), and 45Z eligibility require registration + tax counsel.</t>
+          <t>Confirmed support letters on file: Geocycle (Paolo Carollo) 1/26/26; U-Arizona (Dr. Joel Cuello) 2/10/26;</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Securities offering: not an offer; counsel review required; PublicLogic = governance, NOT placement agent; fee fixed/non-contingent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * Figures trace to the canonical workbook / signed pro forma; verify before circulation.</t>
+          <t xml:space="preserve">  Acadia/Brien Walton validation 5/8/26; WasteWerx mutual NDA executed 5/18/26.</t>
         </is>
       </c>
     </row>
@@ -686,11 +684,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="52" customWidth="1" min="5" max="5"/>
@@ -699,14 +697,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Inputs — editable assumptions (per site)</t>
+          <t>Inputs — signed-document values (Canonical v2.0)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Edit yellow cells; everything else recalculates. [CONFIRM] = verify before investor use.</t>
+          <t>Yellow = editable. Revenue &amp; Pro Forma opex are executed-Pro-Forma values; stress levers are the diligence swings.</t>
         </is>
       </c>
     </row>
@@ -733,173 +731,173 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Source / note</t>
+          <t>Source</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>tpd</t>
+          <t>rd_sales</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Feedstock throughput</t>
+          <t>RD fuel sales (2,399,040 gal x $2.00)</t>
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>100</v>
+        <v>4798080</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>MT/day</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>WasteWerx model</t>
+          <t>Canonical Revenue B10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>saf_sales</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Operating days</t>
+          <t>SAF fuel sales (2,301,120 gal x $4.50)</t>
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>300</v>
+        <v>10355040</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>days/yr</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>WasteWerx model</t>
+          <t>Canonical Revenue B11</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>oil_yield</t>
+          <t>d4_rin</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Oil/fuel yield</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>0.45</v>
+          <t>D4 RIN — RD ($2.00/gal)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>4798080</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>of feedstock</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>WasteWerx model</t>
+          <t>Canonical Revenue B12 — Flag 3 (RFS)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>cb_yield</t>
+          <t>d7_rin</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Carbon black yield</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>0.45</v>
+          <t>D7 RIN — SAF ($4.00/gal)</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>9204480</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>of feedstock</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>WasteWerx model</t>
+          <t>Canonical Revenue B13 — Flag 3 (RFS)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>oil_price</t>
+          <t>z45_rd</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Pyrolysis oil price (conservative/market)</t>
+          <t>Section 45Z — RD ($1.00/gal)</t>
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>500</v>
+        <v>2399040</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>$/MT</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>market-grounded base [CONFIRM contract]</t>
+          <t>Canonical Revenue B14 — Flag 3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>cb_price</t>
+          <t>z45_saf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Carbon black price</t>
+          <t>Section 45Z — SAF ($1.75/gal)</t>
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>750</v>
+        <v>4026960</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>$/MT</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>[CONFIRM market price + offtake]</t>
+          <t>Canonical Revenue B15 — Flag 3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>fuel_base</t>
+          <t>cb_upside</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>WasteWerx fuel revenue (distilled RD+SAF, base)</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>22181680</v>
+          <t>Carbon black (UPSIDE, excluded from base)</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>0</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -908,23 +906,23 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED: $35,581,680 total minus ~$13.4M credits (13_Financial_Reconciliation)</t>
+          <t>Canonical Flag 1; deck implied ~$10.125M — uncontracted</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>credits</t>
+          <t>ww_fees</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RIN + Section 45Z (CONTINGENT)</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="n">
-        <v>13400000</v>
+          <t>WasteWerx fees (monitoring $420k + royalty $2,820,096)</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>3240096</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -933,23 +931,23 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>CONFIRMED contingent: '$13.4M+/yr requires EPA RFS registration — NOT guaranteed'</t>
+          <t>Canonical Per-Site P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>labor_fl</t>
+          <t>feedstock_pf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Site labor — total loaded, 62 FTE (FL basis)</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>5522400</v>
+          <t>Feedstock — Pro Forma ($0.20/gal)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>940032</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -958,73 +956,73 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>WasteWerx Staffing Pro Forma (uploaded); FL market</t>
+          <t>Canonical Per-Site P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>mi_adj</t>
+          <t>utilities</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Michigan labor adjustment factor</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>1.05</v>
+          <t>Utilities ($0.05/gal)</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>235008</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>FL-&gt;MI cost-of-living [Robert to set]</t>
+          <t>Canonical Per-Site P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>xtrain</t>
+          <t>distribution</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cross-training / headcount efficiency factor</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="n">
-        <v>1</v>
+          <t>Fuel distribution &amp; shipping ($0.08/gal)</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>376013</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>x</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>WasteWerx (V.Tizio 5/27): staffing is WORST-CASE; cross-training reduces it [set &lt;1.0]</t>
+          <t>Canonical Per-Site P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>feedstock</t>
+          <t>labor_pf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Feedstock cost (tires) — co-location may reduce</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>3720000</v>
+          <t>Operating labor — Pro Forma (4 FTE + manager)</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>425000</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1033,98 +1031,98 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>deck Operating Savings tab; co-loc w/ ERR/Geocycle may cut this — BIGGEST swing</t>
+          <t>Canonical Per-Site P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>royalty_gal</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>WasteWerx production royalty rate</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="n">
-        <v>0.6</v>
+          <t>Insurance (GL + property)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>65000</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>$/gal</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>WasteWerx Model 3 (executed)</t>
+          <t>Canonical Per-Site P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>annual_gal</t>
+          <t>permits</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Annual fuel output (85% util)</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="n">
-        <v>4467600</v>
+          <t>Permit renewals &amp; compliance</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>25000</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>gal/yr</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>WasteWerx Model 3</t>
+          <t>Canonical Per-Site P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>monitor_mo</t>
+          <t>ga</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>WasteWerx monitoring fee</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="n">
-        <v>35000</v>
+          <t>G&amp;A overhead</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>75000</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>$/mo</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>WasteWerx Model 3 (CPI-indexed)</t>
+          <t>Canonical Per-Site P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>utilities</t>
+          <t>labor_real</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Utilities (electric+water+fees)</t>
-        </is>
-      </c>
-      <c r="C20" s="8" t="n">
-        <v>96960</v>
+          <t>Operating labor — STAFFING pro forma (62 FTE)</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>5522400</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1133,73 +1131,73 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>deck Operating Savings tab</t>
+          <t>WasteWerx Staffing Pro Forma (worst-case; cross-train reduces)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>maint</t>
+          <t>mi_adj</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Maintenance + parts</t>
+          <t>Michigan labor adjustment</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>42000</v>
+        <v>1.05</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>$/yr</t>
+          <t>x</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>deck Operating Savings tab [low for plant scale — confirm]</t>
+          <t>FL-&gt;MI [Robert]</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>xtrain</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Cross-training factor (&lt;1.0 reduces)</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>78000</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>$/yr</t>
+          <t>x</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>deck Operating Savings tab</t>
+          <t>Vincent Tizio 5/27: staffing is worst-case</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>property_tax</t>
+          <t>feedstock_real</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Property tax</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n">
-        <v>168000</v>
+          <t>Feedstock — operator reality</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>3720000</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1208,382 +1206,132 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>deck Operating Savings tab</t>
+          <t>Deck $200/ton landed; vs ERR $25/ton tipping = ~$1M [CONFIRM]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>security</t>
+          <t>y1_cashout</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>360000</v>
+          <t>Year 1 cash out (WasteWerx $6,670,328 + capex $952,500)</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>7622828</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>$/yr</t>
+          <t>$</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>deck Operating Savings tab</t>
+          <t>Canonical — CONFIRMED</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>legal_acct</t>
+          <t>raise_site</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Legal + accounting (with PublicLogic)</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="n">
-        <v>750000</v>
+          <t>Project raise per site</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>15000000</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>$/yr</t>
+          <t>$</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>deck Operating Savings tab (revised)</t>
+          <t>sponsor</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>pl_gov</t>
+          <t>company_raise</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PublicLogic governance retainer</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="n">
-        <v>120000</v>
+          <t>Company-level raise (separate)</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>2500000</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>$/yr</t>
+          <t>$</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>deck ($10k/mo)</t>
+          <t>sponsor</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>raise_site</t>
+          <t>comm_share</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Project raise per site</t>
+          <t>Community profit share (of EBITDA)</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>15000000</v>
+        <v>0.1</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>of EBITDA</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>sponsor-directed headline</t>
+          <t>Canonical — contractual, locally directed</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>build</t>
+          <t>sites</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Use of funds: build / core plant</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="n">
-        <v>8000000</v>
+          <t>Sites in corridor</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>$</t>
+          <t>#</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>rough verbal</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>addl</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Use of funds: added construction</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>rough verbal</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>preproc</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Use of funds: pre-processing/pre-treatment equip</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>rough verbal</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>conting</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Use of funds: contingency/fees/payroll/training</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>rough verbal</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>ww_license</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>WasteWerx license fee (Yr1, net of design credit)</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n">
-        <v>5450000</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>signed Model 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>ww_design</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>WasteWerx design fee (credited)</t>
-        </is>
-      </c>
-      <c r="C33" s="8" t="n">
-        <v>50000</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>signed Model 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>ww_monitor</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>WasteWerx Yr1 monitoring fees</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="n">
-        <v>175000</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>signed Model 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>ww_royalty</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>WasteWerx Yr1 production royalty</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="n">
-        <v>995328</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>signed Model 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>cust_capex</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Customer-side capex (site/utilities/permits/WC)</t>
-        </is>
-      </c>
-      <c r="C36" s="8" t="n">
-        <v>952500</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>signed Model 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>company_raise</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Company-level raise (separate)</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="n">
-        <v>2500000</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>sponsor-directed</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>sites</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Number of sites in network</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Michigan corridor</t>
+          <t>Lincoln/Flint/Coleman (Coldwater = Phase 2)</t>
         </is>
       </c>
     </row>
@@ -1598,283 +1346,229 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Annual operating cost — bottom-up (per site, steady state)</t>
+          <t>Revenue build-up (Canonical Revenue tab — executed Pro Forma)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>KEY FINDING: site labor ALONE exceeds the signed model's entire implied opex. Green = known, orange = estimate to confirm.</t>
+          <t>Green = base fuel (sells today). Orange = contingent credits (RFS/45Z). Carbon black = $0 base (Flag 1).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Cost line</t>
+          <t>Stream</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Amount $/yr</t>
+          <t>$/yr</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Site labor — loaded (62 FTE worst-case x MI-adj x cross-training)</t>
+          <t>Renewable diesel sales</t>
         </is>
       </c>
       <c r="B5" s="10">
-        <f>Inputs!$C$13*Inputs!$C$14*Inputs!$C$15</f>
-        <v/>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>WORST-CASE per WasteWerx (V.Tizio); benefits/MI rates need actuals [Robert]</t>
+        <f>Inputs!$C$5</f>
+        <v/>
+      </c>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>BASE FUEL</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>2,399,040 gal x $2.00 — sells on contract/market</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>WasteWerx royalty (steady-state, $0.60/gal x output)</t>
+          <t>SAF / kerosene sales</t>
         </is>
       </c>
       <c r="B6" s="10">
-        <f>Inputs!$C$17*Inputs!$C$18</f>
-        <v/>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>WasteWerx Model 3 — capital-bridge uses Yr1 partial</t>
+        <f>Inputs!$C$6</f>
+        <v/>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>BASE FUEL</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>2,301,120 gal x $4.50 — confirm SAF offtake + classification</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>WasteWerx monitoring ($35k/mo x 12)</t>
-        </is>
-      </c>
-      <c r="B7" s="10">
-        <f>Inputs!$C$19*12</f>
-        <v/>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>WasteWerx Model 3</t>
+          <t>D4 RIN — RD</t>
+        </is>
+      </c>
+      <c r="B7" s="12">
+        <f>Inputs!$C$7</f>
+        <v/>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>CONTINGENT</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>RFS registration required (Flag 3)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Feedstock cost (tires)</t>
-        </is>
-      </c>
-      <c r="B8" s="11">
-        <f>Inputs!$C$16</f>
-        <v/>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>deck; co-loc w/ ERR/Geocycle may reduce — BIGGEST swing</t>
+          <t>D7 RIN — SAF</t>
+        </is>
+      </c>
+      <c r="B8" s="12">
+        <f>Inputs!$C$8</f>
+        <v/>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>CONTINGENT</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>RFS registration required (Flag 3)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Utilities (electric+water+fees)</t>
-        </is>
-      </c>
-      <c r="B9" s="10">
-        <f>Inputs!$C$20</f>
-        <v/>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>deck Operating Savings tab</t>
+          <t>Section 45Z — RD</t>
+        </is>
+      </c>
+      <c r="B9" s="12">
+        <f>Inputs!$C$9</f>
+        <v/>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>CONTINGENT</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>45Z qualification + tax counsel (Flag 3)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Maintenance + parts</t>
-        </is>
-      </c>
-      <c r="B10" s="10">
-        <f>Inputs!$C$21</f>
-        <v/>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>deck [low for scale — confirm]</t>
+          <t>Section 45Z — SAF</t>
+        </is>
+      </c>
+      <c r="B10" s="12">
+        <f>Inputs!$C$10</f>
+        <v/>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>CONTINGENT</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>45Z qualification + tax counsel (Flag 3)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="B11" s="10">
-        <f>Inputs!$C$22</f>
-        <v/>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>deck Operating Savings tab</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Property tax</t>
-        </is>
-      </c>
-      <c r="B12" s="10">
-        <f>Inputs!$C$23</f>
-        <v/>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>deck Operating Savings tab</t>
+          <t>Carbon black</t>
+        </is>
+      </c>
+      <c r="B11" s="6">
+        <f>Inputs!$C$11</f>
+        <v/>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>UPSIDE</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>$0 in executed Pro Forma (Flag 1); deck ~$10.125M — uncontracted</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="B13" s="10">
-        <f>Inputs!$C$24</f>
-        <v/>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>deck Operating Savings tab</t>
-        </is>
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Base fuel (RD+SAF)</t>
+        </is>
+      </c>
+      <c r="B13" s="14">
+        <f>B5+B6</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Legal + accounting (with PublicLogic)</t>
-        </is>
-      </c>
-      <c r="B14" s="10">
-        <f>Inputs!$C$25</f>
-        <v/>
-      </c>
-      <c r="C14" s="9" t="inlineStr">
-        <is>
-          <t>deck Operating Savings tab (revised)</t>
-        </is>
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Contingent credits (RIN+45Z)</t>
+        </is>
+      </c>
+      <c r="B14" s="15">
+        <f>B7+B8+B9+B10</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>PublicLogic governance retainer</t>
-        </is>
-      </c>
-      <c r="B15" s="10">
-        <f>Inputs!$C$26</f>
-        <v/>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>deck ($10k/mo)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>TOTAL ANNUAL OPEX (bottom-up)</t>
-        </is>
-      </c>
-      <c r="B16" s="13">
-        <f>SUM(B5:B15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>Signed model's IMPLIED opex (rev - EBITDA)</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="n">
-        <v>5381149</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Understatement baked into signed EBITDA (bottom-up - implied)</t>
-        </is>
-      </c>
-      <c r="B19" s="16">
-        <f>B16-B18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Labor ALONE (MI-adj x cross-training)</t>
-        </is>
-      </c>
-      <c r="B21" s="17">
-        <f>Inputs!$C$13*Inputs!$C$14*Inputs!$C$15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>-&gt; at worst-case staffing, labor alone exceeds the signed model's entire implied opex. Signed EBITDA overstates margin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>WasteWerx (V. Tizio, 5/27/26): staffing is intentional worst-case 'overkill'; cross-trained roles will reduce headcount;</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>health insurance &amp; benefits need actuals; salaries are FL market — Robert to adjust to Michigan pay rates. Flex via xtrain + mi_adj inputs.</t>
-        </is>
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL REVENUE (Pro Forma)</t>
+        </is>
+      </c>
+      <c r="B15" s="16">
+        <f>B13+B14+B11</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1888,355 +1582,235 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Per-site revenue build-up, scenarios &amp; capital bridge</t>
+          <t>Operating cost — two cases (the diligence swing)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Line-by-line build-up (the answer to 'show me $6.75M fuel -&gt; $35.58M, line by line'). Base = green, contingent = orange.</t>
+          <t>Pro Forma (as signed, 5 FTE / $0.20-gal feedstock) vs Operator-reality (62-FTE staffing + real feedstock).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Revenue line</t>
+          <t>Line</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Amount $/yr</t>
+          <t>Pro Forma (signed)</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Operator-reality</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Status / caveat</t>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>WasteWerx fuel (distilled RD+SAF)</t>
-        </is>
-      </c>
-      <c r="B5" s="10">
-        <f>Inputs!$C$11</f>
-        <v/>
-      </c>
-      <c r="C5" s="19" t="inlineStr">
-        <is>
-          <t>BASE</t>
-        </is>
+          <t>WasteWerx fees (monitoring+royalty)</t>
+        </is>
+      </c>
+      <c r="B5" s="17">
+        <f>Inputs!$C$12</f>
+        <v/>
+      </c>
+      <c r="C5" s="17">
+        <f>Inputs!$C$12</f>
+        <v/>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>CONFIRMED: $35.58M total minus ~$13.4M credits (13_Financial_Reconciliation)</t>
+          <t>same</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Carbon black (deck-era; additive?)</t>
-        </is>
-      </c>
-      <c r="B6" s="10">
-        <f>(Inputs!$C$5*Inputs!$C$6*Inputs!$C$8)*Inputs!$C$10</f>
-        <v/>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>ADD'L (contingent)</t>
-        </is>
+          <t>Feedstock</t>
+        </is>
+      </c>
+      <c r="B6" s="12">
+        <f>Inputs!$C$13</f>
+        <v/>
+      </c>
+      <c r="C6" s="12">
+        <f>Inputs!$C$23</f>
+        <v/>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>$0 in executed WasteWerx pro forma — confirm if additive + offtake before use</t>
+          <t>PF $0.20/gal vs deck $200/ton; ERR tipping $25/ton ~ $1M — SWING</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>RIN + Section 45Z (credits)</t>
-        </is>
-      </c>
-      <c r="B7" s="11">
-        <f>Inputs!$C$12</f>
-        <v/>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
-        <is>
-          <t>CONTINGENT UPSIDE</t>
-        </is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="B7" s="17">
+        <f>Inputs!$C$14</f>
+        <v/>
+      </c>
+      <c r="C7" s="17">
+        <f>Inputs!$C$14</f>
+        <v/>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>CONFIRMED contingent: ~$13.4M+; requires EPA RFS registration — NOT guaranteed</t>
-        </is>
+          <t>same</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Fuel distribution &amp; shipping</t>
+        </is>
+      </c>
+      <c r="B8" s="17">
+        <f>Inputs!$C$15</f>
+        <v/>
+      </c>
+      <c r="C8" s="17">
+        <f>Inputs!$C$15</f>
+        <v/>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Operating labor</t>
+        </is>
+      </c>
+      <c r="B9" s="12">
+        <f>Inputs!$C$16</f>
+        <v/>
+      </c>
+      <c r="C9" s="12">
+        <f>Inputs!$C$20*Inputs!$C$21*Inputs!$C$22</f>
+        <v/>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>PF 5 FTE $425k vs staffing 62 FTE $5.52M — BIGGEST SWING</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B10" s="17">
+        <f>Inputs!$C$17</f>
+        <v/>
+      </c>
+      <c r="C10" s="17">
+        <f>Inputs!$C$17</f>
+        <v/>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Permit renewals &amp; compliance</t>
+        </is>
+      </c>
+      <c r="B11" s="17">
+        <f>Inputs!$C$18</f>
+        <v/>
+      </c>
+      <c r="C11" s="17">
+        <f>Inputs!$C$18</f>
+        <v/>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>G&amp;A overhead</t>
+        </is>
+      </c>
+      <c r="B12" s="17">
+        <f>Inputs!$C$19</f>
+        <v/>
+      </c>
+      <c r="C12" s="17">
+        <f>Inputs!$C$19</f>
+        <v/>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>same</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL OPEX</t>
+        </is>
+      </c>
+      <c r="B13" s="14">
+        <f>SUM(B5:B12)</f>
+        <v/>
+      </c>
+      <c r="C13" s="15">
+        <f>SUM(C5:C12)</f>
+        <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>SCENARIO SUMMARY (per site)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Revenue $/yr</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Opex $/yr</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>EBITDA $/yr</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>Credits in headline?</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Base — WasteWerx fuel only (no credits, no CB)</t>
-        </is>
-      </c>
-      <c r="B16" s="20">
-        <f>B5</f>
-        <v/>
-      </c>
-      <c r="C16" s="20">
-        <f>Opex_BuildUp!$B$16</f>
-        <v/>
-      </c>
-      <c r="D16" s="21">
-        <f>B16-C16</f>
-        <v/>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>No — most defensible</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Base + carbon black (if additive)</t>
-        </is>
-      </c>
-      <c r="B17" s="20">
-        <f>B5+B6</f>
-        <v/>
-      </c>
-      <c r="C17" s="20">
-        <f>Opex_BuildUp!$B$16</f>
-        <v/>
-      </c>
-      <c r="D17" s="21">
-        <f>B17-C17</f>
-        <v/>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>No (CB itself contingent)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>WasteWerx confirmed headline (fuel + credits, no CB)</t>
-        </is>
-      </c>
-      <c r="B18" s="20">
-        <f>B5+B7</f>
-        <v/>
-      </c>
-      <c r="C18" s="20">
-        <f>Opex_BuildUp!$B$16</f>
-        <v/>
-      </c>
-      <c r="D18" s="22">
-        <f>B18-C18</f>
-        <v/>
-      </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>YES — ~$13.4M credit-dependent</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Full stack (fuel + carbon black + credits)</t>
-        </is>
-      </c>
-      <c r="B19" s="20">
-        <f>B5+B6+B7</f>
-        <v/>
-      </c>
-      <c r="C19" s="20">
-        <f>Opex_BuildUp!$B$16</f>
-        <v/>
-      </c>
-      <c r="D19" s="22">
-        <f>B19-C19</f>
-        <v/>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Contingent credit value at risk in headline (RIN + 45Z)</t>
-        </is>
-      </c>
-      <c r="B21" s="16">
-        <f>B7</f>
-        <v/>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>&lt;- this much of the signed headline is NOT secured</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>PER-SITE CAPITAL BRIDGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Project raise per site</t>
-        </is>
-      </c>
-      <c r="B24" s="15">
-        <f>Inputs!$C$27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>WasteWerx Year 1 (license+design+monitoring+royalty)</t>
-        </is>
-      </c>
-      <c r="B25" s="15">
-        <f>Inputs!$C$32+Inputs!$C$33+Inputs!$C$34+Inputs!$C$35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Customer-side capex</t>
-        </is>
-      </c>
-      <c r="B26" s="15">
-        <f>Inputs!$C$36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>Total Year 1 cash out</t>
-        </is>
-      </c>
-      <c r="B27" s="17">
-        <f>B25+B26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="14" t="inlineStr">
-        <is>
-          <t>Residual project envelope (land, civil, integration, contingency, payroll, reserves)</t>
-        </is>
-      </c>
-      <c r="B28" s="13">
-        <f>B24-B27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Use-of-funds (sponsor rough) vs raise — RECONCILE</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Build + added construction + pre-processing + contingency</t>
-        </is>
-      </c>
-      <c r="B31" s="15">
-        <f>Inputs!$C$28+Inputs!$C$29+Inputs!$C$30+Inputs!$C$31</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Reconciliation gap vs $15M raise (negative = over)</t>
-        </is>
-      </c>
-      <c r="B32" s="23">
-        <f>Inputs!$C$27-B31</f>
-        <v/>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>[CONFIRM which line absorbs the ~$1M]</t>
-        </is>
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>Delta (operator-reality - pro forma)</t>
+        </is>
+      </c>
+      <c r="C14" s="18">
+        <f>C13-B13</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2250,223 +1824,163 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Three-site network rollup (live x number of sites)</t>
+          <t>EBITDA matrix — revenue case x opex case (the honest range)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Base anchors; credits flagged. Company raise kept separate.</t>
+          <t>Pro Forma-as-signed is one cell. The rest is the diligence reality. Community share = 10% of EBITDA.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Revenue case</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Per site</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>x Sites</t>
+          <t>Opex (Pro Forma)</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Network total</t>
+          <t>EBITDA (PF)</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Opex (Operator)</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>EBITDA (Operator)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Base EBITDA — Conservative</t>
-        </is>
-      </c>
-      <c r="B5" s="20">
-        <f>'Per_Site'!D16</f>
-        <v/>
-      </c>
-      <c r="C5" s="19">
-        <f>Inputs!$C$38</f>
-        <v/>
-      </c>
-      <c r="D5" s="21">
-        <f>B5*C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>BASE — defensible</t>
-        </is>
+          <t>Base fuel only (no credits, no CB)</t>
+        </is>
+      </c>
+      <c r="B5" s="17">
+        <f>Revenue!$B$13</f>
+        <v/>
+      </c>
+      <c r="C5" s="17">
+        <f>Opex!$B$13</f>
+        <v/>
+      </c>
+      <c r="D5" s="19">
+        <f>B5-C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="17">
+        <f>Opex!$C$13</f>
+        <v/>
+      </c>
+      <c r="F5" s="20">
+        <f>B5-E5</f>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Base EBITDA — Upgraded</t>
-        </is>
-      </c>
-      <c r="B6" s="20">
-        <f>'Per_Site'!D17</f>
-        <v/>
-      </c>
-      <c r="C6" s="19">
-        <f>Inputs!$C$38</f>
-        <v/>
-      </c>
-      <c r="D6" s="21">
-        <f>B6*C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>BASE — needs distillation+offtake</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Signed-headline EBITDA (credit-dependent)</t>
-        </is>
-      </c>
-      <c r="B7" s="20">
-        <f>'Per_Site'!D18</f>
-        <v/>
-      </c>
-      <c r="C7" s="19">
-        <f>Inputs!$C$38</f>
-        <v/>
-      </c>
-      <c r="D7" s="22">
-        <f>B7*C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>CONTINGENT — ~$20.4M/site credits</t>
-        </is>
+          <t>Fuel + credits (Pro Forma total)</t>
+        </is>
+      </c>
+      <c r="B6" s="17">
+        <f>Revenue!$B$15</f>
+        <v/>
+      </c>
+      <c r="C6" s="17">
+        <f>Opex!$B$13</f>
+        <v/>
+      </c>
+      <c r="D6" s="19">
+        <f>B6-C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="17">
+        <f>Opex!$C$13</f>
+        <v/>
+      </c>
+      <c r="F6" s="20">
+        <f>B6-E6</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Signed-headline revenue</t>
-        </is>
-      </c>
-      <c r="B8" s="20">
-        <f>'Per_Site'!B18</f>
-        <v/>
-      </c>
-      <c r="C8" s="19">
-        <f>Inputs!$C$38</f>
-        <v/>
-      </c>
-      <c r="D8" s="22">
-        <f>B8*C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>CONTINGENT</t>
-        </is>
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>SIGNED HEADLINE = Fuel+credits @ Pro Forma opex</t>
+        </is>
+      </c>
+      <c r="B8" s="21">
+        <f>Revenue!$B$15</f>
+        <v/>
+      </c>
+      <c r="D8" s="16">
+        <f>D6</f>
+        <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Contingent credit value at risk</t>
-        </is>
-      </c>
-      <c r="B9" s="20">
-        <f>'Per_Site'!B21</f>
-        <v/>
-      </c>
-      <c r="C9" s="19">
-        <f>Inputs!$C$38</f>
-        <v/>
-      </c>
-      <c r="D9" s="22">
-        <f>B9*C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>NOT secured</t>
-        </is>
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>DILIGENCE REALITY = Fuel+credits @ operator opex</t>
+        </is>
+      </c>
+      <c r="F9" s="22">
+        <f>F6</f>
+        <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Year 1 cash out</t>
-        </is>
-      </c>
-      <c r="B10" s="20">
-        <f>'Per_Site'!B27</f>
-        <v/>
-      </c>
-      <c r="C10" s="19">
-        <f>Inputs!$C$38</f>
-        <v/>
-      </c>
-      <c r="D10" s="21">
-        <f>B10*C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Project raises (sites x $15M)</t>
-        </is>
-      </c>
-      <c r="B11" s="20">
-        <f>'Per_Site'!B24</f>
-        <v/>
-      </c>
-      <c r="C11" s="19">
-        <f>Inputs!$C$38</f>
-        <v/>
-      </c>
-      <c r="D11" s="21">
-        <f>B11*C11</f>
-        <v/>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>excludes company raise</t>
-        </is>
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>WITHOUT CREDITS @ operator opex (the floor)</t>
+        </is>
+      </c>
+      <c r="F10" s="23">
+        <f>F5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>Community profit share (10% of signed EBITDA)</t>
+        </is>
+      </c>
+      <c r="D12" s="21">
+        <f>D6*Inputs!$C$27</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2480,107 +1994,144 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The two raises — kept distinct</t>
+          <t>3-site corridor rollup (Lincoln/Flint/Coleman)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Site capital != company capital. Never blend.</t>
+          <t>Both the signed headline and the operator-reality EBITDA, x3.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Item</t>
+          <t>Metric</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Amount</t>
+          <t>Per site</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>x Sites</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Corridor total</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
-        <is>
-          <t>Project raise per site</t>
-        </is>
-      </c>
-      <c r="B5" s="25">
-        <f>Inputs!$C$27</f>
-        <v/>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>site deployment</t>
-        </is>
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Total revenue (Pro Forma)</t>
+        </is>
+      </c>
+      <c r="B5" s="17">
+        <f>Revenue!$B$15</f>
+        <v/>
+      </c>
+      <c r="C5" s="11">
+        <f>Inputs!$C$28</f>
+        <v/>
+      </c>
+      <c r="D5" s="24">
+        <f>B5*C5</f>
+        <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
-        <is>
-          <t>Project raises — 3 sites</t>
-        </is>
-      </c>
-      <c r="B6" s="25">
-        <f>Inputs!$C$27*Inputs!$C$38</f>
-        <v/>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>excludes company raise</t>
-        </is>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>EBITDA — signed (PF opex)</t>
+        </is>
+      </c>
+      <c r="B6" s="17">
+        <f>'P&amp;L'!D6</f>
+        <v/>
+      </c>
+      <c r="C6" s="11">
+        <f>Inputs!$C$28</f>
+        <v/>
+      </c>
+      <c r="D6" s="19">
+        <f>B6*C6</f>
+        <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
-        <is>
-          <t>Company-level raise (separate)</t>
-        </is>
-      </c>
-      <c r="B7" s="25">
-        <f>Inputs!$C$37</f>
-        <v/>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>working capital, payroll, PublicLogic gov fees, team buildout [CONFIRM split]</t>
-        </is>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>EBITDA — operator-reality</t>
+        </is>
+      </c>
+      <c r="B7" s="17">
+        <f>'P&amp;L'!F6</f>
+        <v/>
+      </c>
+      <c r="C7" s="11">
+        <f>Inputs!$C$28</f>
+        <v/>
+      </c>
+      <c r="D7" s="20">
+        <f>B7*C7</f>
+        <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>Combined discussion envelope</t>
-        </is>
-      </c>
-      <c r="B8" s="25">
-        <f>Inputs!$C$27*Inputs!$C$38+Inputs!$C$37</f>
-        <v/>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>present asks separately</t>
-        </is>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>EBITDA — base fuel only @ operator opex</t>
+        </is>
+      </c>
+      <c r="B8" s="17">
+        <f>'P&amp;L'!F5</f>
+        <v/>
+      </c>
+      <c r="C8" s="11">
+        <f>Inputs!$C$28</f>
+        <v/>
+      </c>
+      <c r="D8" s="20">
+        <f>B8*C8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Year 1 cash out</t>
+        </is>
+      </c>
+      <c r="B9" s="17">
+        <f>Inputs!$C$24</f>
+        <v/>
+      </c>
+      <c r="C9" s="11">
+        <f>Inputs!$C$28</f>
+        <v/>
+      </c>
+      <c r="D9" s="24">
+        <f>B9*C9</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2594,245 +2145,309 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="116" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="56" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Caveats &amp; confirm-before-send</t>
+          <t>Capital &amp; the two raises</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Every contingent assumption and open item. Investor headline must lead with the base case.</t>
+          <t>Site capital != company capital. Year 1 cash out is confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>Year 1 cash out per site</t>
+        </is>
+      </c>
+      <c r="B5" s="26">
+        <f>Inputs!$C$24</f>
+        <v/>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>CONFIRMED (WasteWerx $6,670,328 + capex $952,500)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="25" t="inlineStr">
+        <is>
+          <t>Project raise per site</t>
+        </is>
+      </c>
+      <c r="B6" s="26">
+        <f>Inputs!$C$25</f>
+        <v/>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>sponsor headline</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>Project raises — 3 sites</t>
+        </is>
+      </c>
+      <c r="B7" s="26">
+        <f>Inputs!$C$25*Inputs!$C$28</f>
+        <v/>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>excludes company raise</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="25" t="inlineStr">
+        <is>
+          <t>Company-level raise (separate)</t>
+        </is>
+      </c>
+      <c r="B8" s="26">
+        <f>Inputs!$C$26</f>
+        <v/>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>working capital, payroll, PL gov, team [CONFIRM split]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>Combined discussion envelope</t>
+        </is>
+      </c>
+      <c r="B9" s="26">
+        <f>Inputs!$C$25*Inputs!$C$28+Inputs!$C$26</f>
+        <v/>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>present asks separately</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="120" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Open items (commercial, not modeling) + structure flags + support letters</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>From Canonical Flags + Reconciliation discrepancy log + Investor Brief.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>HEADLINE DISCIPLINE</t>
+          <t>REVENUE / OPEX (the diligence questions)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Investor-facing headline = BASE EBITDA (fuel + carbon black). Show RIN + 45Z as separately-labeled contingent upside.</t>
+          <t xml:space="preserve">  * Flag 1 — Carbon black: $0 in executed Pro Forma; deck implied ~$10.125M. Feedstock Yield Model rates tires 32% carbon</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Signed-model EBITDA (~$30.2M/site) is ~$20.4M dependent on RIN + 45Z. Do NOT anchor the deck on it unproven.</t>
+          <t xml:space="preserve">    co-product (graphene-precursor grade) — REAL but UNCONTRACTED. Upside only until grade + price contracted.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Flag 3 — RFS / 45Z: $20,428,560 of the $35.58M is RIN + 45Z. Requires EPA RFS pathway petition + 3rd-party engineering</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>CONTINGENT / REGULATORY</t>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    review + favorable 45Z CI. Without registration, this revenue does not exist. Phase 1 workstream.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * D4/D7 RIN: requires EPA RFS pathway registration; volumes &amp; prices [CONFIRM].</t>
+          <t xml:space="preserve">  * STAFFING TENSION: Pro Forma opex uses 4 FTE + manager ($425k); WasteWerx STAFFING pro forma says 62 FTE ($5.52M).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Section 45Z (RD + SAF): requires eligibility determination + tax counsel; rate assumption [CONFIRM].</t>
+          <t xml:space="preserve">    This single swing moves EBITDA from $30.2M (signed) to ~$22M (operator-reality). Resolve actual headcount with WasteWerx.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * SAF/kerosene product classification [CONFIRM] — drives both fuel revenue and 45Z.</t>
+          <t xml:space="preserve">  * FEEDSTOCK SWING: Pro Forma $0.20/gal ($940k) vs deck $200/ton ($3.72M) vs ERR $25/ton tipping (~$1M). Confirm with Robert.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * Carbon black: included in base as a real product; price + offtake [CONFIRM]. (Signed model excluded it.)</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * OPEX IS NOW SOURCED (bottom-up ~$14.2M/site) from the WasteWerx staffing pro forma + deck Operating Savings tab +</t>
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>STRUCTURE / LEGAL (Canonical AUTHORITY/TRANSFER flags)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    WasteWerx Model 3 terms — vs the signed model's implied $5.38M. Understatement ~$8.85M.</t>
+          <t xml:space="preserve">  * Flag 2 — License NOT depreciable: title stays with WasteWerx; no transfer on EM&amp;S dissolution. Brief Walton before any</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * THE $30.2M EBITDA IS WASTEWERX-SCOPE: it sits on WasteWerx's confirmed $5.38M opex (fees + minimal ops) which OMITS the</t>
+          <t xml:space="preserve">    DCF/investor return model. Address transfer in SPV structure. IoT-metered royalty -&gt; audit rights in operating agreement.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    customer's full 62-FTE site labor (~$5.5M) and feedstock (~$1-3.7M). On the customer's all-in opex (~$14.2M) the SAME</t>
+          <t xml:space="preserve">  * MAR Year 1 = 70% of nameplate (not 80%); Year 2+ = 80%. Early termination after Yr3: current MAR + 50% next-year MAR.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    $35.58M revenue yields ~$21.35M EBITDA, not $30.2M. (The deck's own reconciled model shows ~$11.2M expenses / ~$5.66M net income.)</t>
+          <t xml:space="preserve">  * Securities: investor structures (deck $3.5M/yr 4yr vs agreement $5M/yr + balloon = $40M) are unreconciled AND likely</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Royalty corrected to STEADY-STATE: $0.60/gal x 4,467,600 gal = ~$2.68M/yr ($995k in the capital bridge is Yr1 partial). Monitoring $420k/yr.</t>
+          <t xml:space="preserve">    securities offerings with no Reg D / PPM / sub docs. Securities counsel before any investor circulation. PL = governance,</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * FEEDSTOCK is a CONFIRMED swing: deck $200/ton landed = $3.72M vs Dort Hwy agreement $25/ton tipping = ~$1M. Resolve with Robert. [CONFIRM]</t>
+          <t xml:space="preserve">    NOT placement agent; fee fixed/non-contingent.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * REVENUE SPLIT NOT IN CANONICAL WORKBOOK: executed pro forma shows only blended 'Fuel+RIN+§45Z' = $35.58M; the RD/SAF/RIN/45Z</t>
+          <t xml:space="preserve">  * Revenue distribution: agreement allocates only 54.5% (Operator 21 + Owner 12 + Supplier 1.5 + REIT 20); 45.5% undefined.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    line items trace to the investor doc, not a source — need the underlying WasteWerx Model 3 to verify the split.</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * CARBON BLACK = $0 in executed WasteWerx model (Disc.#14) but $10.1M in the deck; base case includes it on the DECK assumption — confirm.</t>
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>CONFIRMED SUPPORT / DOCUMENTS ON FILE</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    Labor is worst-case (V. Tizio 5/27): set xtrain (cross-training) + mi_adj (Michigan); benefits actuals pending.</t>
+          <t xml:space="preserve">  * Geocycle (Paolo Carollo) — letter of support 1/26/26. University of Arizona (Dr. Joel Cuello) — support 2/10/26.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Acadia Capital (Brien Walton) — advisory validation 5/8/26. WasteWerx mutual NDA executed 5/18/26.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>CAPITAL</t>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * ERR — 10-yr feedstock supply, 40,000 t/yr at $25/ton tipping (Dort Hwy). Lake State Railway — rail logistics.</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * Sponsor use-of-funds (~$16M) exceeds the $15M/site raise by ~$1M — confirm which line absorbs it.</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * $2.5M company raise stays separate from site SPV totals.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * WasteWerx is a LICENSE, not a sale; title stays with WasteWerx; license fee depreciation differs; transfer/termination terms matter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>GOVERNANCE / LEGAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * Securities: not an offer; securities counsel review required before any circulation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * PublicLogic = governance/document partner, NOT placement agent/broker-dealer; fee FIXED &amp; NON-CONTINGENT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * Community-benefit %: source files say 10%; sponsor flags a conflict — do not publish a number until reconciled.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * Final site list (Coldwater Phase 2 vs Lincoln) [CONFIRM]; parent-holdco legal name [CONFIRM].</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * National Salvage: 'largest treated-wood recycler in the U.S.' unless stronger evidence (a verbal 'in the world' is unverified).</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>Not financial, accounting, securities, or tax advice. Figures trace to the canonical workbook / signed pro forma; verify before use.</t>
+          <t>Not financial/legal/securities/tax advice. Keyed to executed Pro Forma; resolve flags before investor circulation.</t>
         </is>
       </c>
     </row>
